--- a/Screen_7_Cash_Releasing_Benefit/validation_data/stage_7_validation_workbook_full.xlsx
+++ b/Screen_7_Cash_Releasing_Benefit/validation_data/stage_7_validation_workbook_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nhs-my.sharepoint.com/personal/oliver_carey1_nhs_net/Documents/Documents/Projects/NHSCRB/Screen_7_Cash_Releasing_Benefit/validation_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF267FAC-E7CE-4906-8934-5AE241006237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{EF267FAC-E7CE-4906-8934-5AE241006237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{607D2B70-C5E0-4BFA-A9A3-1AF09E5C3831}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{66513E08-89B8-4D61-A86D-819C01466699}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="317">
   <si>
     <t>id</t>
   </si>
@@ -835,9 +835,6 @@
     <t>- Background Early dental decay or demineralised lesions (DLs, also known as white spot lesions) can appear on teeth during fixed orthodontic (brace) treatment. Fluoride reduces decay in susceptible individuals, including orthodontic patients. This review compared various forms of topical fluoride to prevent the development of DLs during orthodontic treatment. This is the second update of the Cochrane Review first published in 2004 and previously updated in 2013. Objectives The primary objective was to evaluate whether topical fluoride reduces the proportion of orthodontic patients with new DLs after fixed appliances. The secondary objectives were to examine the effectiveness of different modes of topical fluoride delivery in reducing the proportions of orthodontic patients with new DLs, as well as the severity of lesions, in terms of number, size and colour. ParticipantÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âassessed outcomes, such as perception of DLs, and oral healthÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Ârelated quality of life data were to be included, as would reports of adverse effects. Search methods Cochrane Oral Health's Information Specialist searched the following databases: Cochrane Oral Health's Trials Register (to 1 February 2019), the Cochrane Central Register of Controlled Trials (CENTRAL; 2019, Issue 1) in the Cochrane Library (searched 1 February 2019), MEDLINE Ovid (1946 to 1 February 2019), and Embase Ovid (1980 to 1 February 2019). The US National Institutes of Health Ongoing Trials Register (ClinicalTrials.gov) and the World Health Organization International Clinical Trials Registry Platform were searched for ongoing trials. No restrictions were placed on the language or date of publication when searching the electronic databases. Selection criteria ParallelÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âgroup, randomised controlled trials comparing the use of a fluorideÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcontaining product versus a placebo, no treatment or a different type of fluoride treatment, in which the outcome of enamel demineralisation was assessed at the start and at the end of orthodontic treatment. Data collection and analysis At least two review authors independently, in duplicate, conducted risk of bias assessments and extracted data. Authors of trials were contacted to obtain missing data or to ask for clarification of aspects of trial methodology. Cochrane's statistical guidelines were followed. Main results This update includes 10 studies and contains data from nine studies, comparing eight interventions, involving 1798 randomised participants (1580 analysed). One report contained insufficient information and the authors have been contacted. We assessed two studies as at low risk of bias, six at unclear risk of bias, and two at high risk of bias. Two placebo (nonÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âfluoride) controlled studies, at low risk of bias, investigated the professional application of varnish (7700 or 10,000 parts per million (ppm) fluoride (F)), every six weeks and found insufficient evidence of a difference regarding its effectiveness in preventing new DLs (risk ratio (RR) 0.52, 95% confidence interval (CI) 0.14 to 1.93; 405 participants; lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). One placebo (nonÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âfluoride) controlled study, at unclear risk of bias, provides a low level of certainty that fluoride foam (12,300 ppm F), professionally applied every two months, may reduce the incidence of new DLs (12% versus 49%) after fixed orthodontic treatment (RR 0.26, 95% CI 0.11 to 0.57; 95 participants). One study, at unclear risk of bias, also provides a low level of certainty that use of a highÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âconcentration fluoride toothpaste (5000 ppm F) by patients may reduce the incidence of new DLs (18% versus 27%) compared with a conventional fluoride toothpaste (1450 ppm F) (RR 0.68, 95% CI 0.46 to 1.00; 380 participants). There was no evidence for a difference in the proportions of orthodontic patients with new DLs on the teeth after treatment with fixed orthodontic appliances for the following comparisons:ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨ ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â an amine fluoride and stannous fluoride toothpaste/mouthrinse combination versus a sodium fluoride toothpaste/mouthrinse,ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨ ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â an amine fluoride gel versus a nonÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âfluoride placebo applied by participants at home once a week and by professional application every three months,ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨ ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â resinÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âmodified glass ionomer cement versus lightÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcured composite resin for bonding orthodontic brackets,ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨ ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â a 250 ppm F mouthrinse versus 0 ppm F placebo mouthrinse,ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨ ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â the use of an intraoral fluorideÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âreleasing glass bead device attached to the brace versus a daily fluoride mouthrinse. The last two comparisons involved studies that were assessed at high risk of bias, because a substantial number of participants were lost to followÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âup. Unfortunately, although the internal validity and hence the quality of the studies has improved since the first version of the review, they have compared different interventions; therefore, the findings are only considered to provide low level of certainty, because none has been replicated by followÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âup studies, in different settings, to confirm external validity. A patientÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âreported outcome, such as concern about the aesthetics of any DLs, was still not included as an outcome in any study. Reports of adverse effects from topical fluoride applications were rare and unlikely to be significant. One study involving fluorideÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcontaining glass beads reported numerous breakages. Authors' conclusions This review found a low level of certainty that 12,300 ppm F foam applied by a professional every 6 to 8 weeks throughout fixed orthodontic treatment, might be effective in reducing the proportion of orthodontic patients with new DLs. In addition, there is a low level of certainty that the patient use of a high fluoride toothpaste (5000 ppm F) throughout orthodontic treatment, might be more effective than a conventional fluoride toothpaste. These two comparisons were based on single studies. There was insufficient evidence of a difference regarding the professional application of fluoride varnish (7700 or 10,000 ppm F). Further adequately powered, randomised controlled trials are required to increase the certainty of these findings and to determine the best means of preventing DLs in patients undergoing fixed orthodontic treatment. The most accurate means of assessing adherence with the use of fluoride products by patients and any possible adverse effects also need to be considered. Future studies should follow up participants beyond the end of orthodontic treatment to determine the effect of DLs on patient satisfaction with treatment. Plain language summary Fluorides for preventing early tooth decay (demineralised lesions) during fixed brace treatment Review question ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨ Ugly white or brown marks sometimes appear on the teeth during treatment with braces to straighten teeth. These are due to early tooth decay and usually occur with fixed, gluedÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âon 'train track', braces, which make it more difficult to clean the teeth. We know that fluoride in toothpaste helps to prevent tooth decay and think that if extra fluoride is given to people wearing fixed braces, it will protect them from getting these marks. The aim of this Cochrane Oral Health's review was to look at how well fluorides help to prevent early tooth decay during fixed brace treatment and to find out the best way to get fluoride to the teeth. Background ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨ Wearing a fixed brace makes it harder for people to keep their teeth clean and may also cause pain. Pain can make it more difficult for people to brush their teeth. This can lead to a buildÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âup of dental plaque around the brackets that attach the fixed brace to the teeth, and if the plaque stays on the tooth for long enough, it will cause early tooth decay, which looks like white or brown marks (demineralised lesions, also known as white spot lesions). People often wear braces for 18 months or longer and if the decay is left to progress, it can cause holes, which are sometimes bad enough to need fillings to be done in the teeth. Fluoride helps the tooth to heal, reducing tooth decay in people who are at risk of developing it. People receiving fixed brace treatment may be given different forms of fluoride treatment. It is important to think about how the fluoride gets to the teeth. Does the fluoride need to be placed by a dentist or dental nurse, or can people having treatment with braces apply the fluoride to their own teeth? Study characteristics ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨ This review is upÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂtoÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âdate as of 1 February 2019. The review includes 10 studies but we could only use the information from nine studies involving 1798 randomised people. We have asked for more information about one study. The review looks at eight different ways of applying fluoride to the teeth. People taking part in the studies were all having treatment with fixed braces. The number of people with new decay on the teeth at end of fixed brace treatment, as well as the amount of decay in each person, were measured and counted. We compared the following treatments:ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨ ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â dentist or nurseÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âapplied fluoride e.g. varnish, gel or foam,ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨ ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â patientÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âapplied/used fluoride e.g. toothpaste, mouthwash, gel or foam, andÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨ ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â materials that release fluoride over time e.g. glues, elastic bands. Key results ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨ One study showed that when the dentist applies a foam with a high level of fluoride in it onto the teeth every time the patient is seen, this might reduce the risk of new decay. Another study found that if patients use a toothpaste with a higher level of fluoride than normal, then this might also reduce the risk of new marks on their teeth. No studies have shown that other ways of giving the teeth extra fluoride reduced the number and/or size of new decay on teeth in people wearing fixed braces. Harmful effects of the different ways of giving the teeth more fluoride were not reported in any of the included studies. Certainty of the evidence ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨ The level of belief we have in these findings is low, due to the lack of studies testing the same fluorides and showing the same results. We suggest that more, wellÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âconducted studies should be done in this area.</t>
   </si>
   <si>
-    <t>The article focuses on clinical outcomes without explicit cash-releasing savings.</t>
-  </si>
-  <si>
     <t>[]</t>
   </si>
   <si>
@@ -853,9 +850,6 @@
     <t>Background: Strategies to control varicella vary across Europe. Evidence from established programmes has prompted the United Kingdom to re-evaluate the need for universal vaccination. The burden of complicated varicella is a key parameter in the cost-effectiveness analysis. Aim(s): Our objective was to estimate the burden of complicated varicella in England. Method(s): This electronic health record surveillance study used data from all NHS hospitals in England to identify varicella admissions between 2004 and 2017. The incidence of pre-defined complications of varicella was estimated using ICD-10 codes. Inpatient costs were calculated based on the payment rules for providers of NHS services. Result(s): There were 61,024 admissions with varicella between 2004 and 2017 and 38.1% had a recognised varicella complication. Incidence of hospitalisation increased by 25% and the proportion with complicated varicella by 24% from 2004/05 to 2016/17. The most common complications were bacterial skin infections (11.25%), pneumonia (4.82%), febrile convulsions (3.39%) and encephalitis (2.44%). Complication rates were higher in older age groups and the type of complications more severe. Length of stay for complicated varicella was 3.1 times longer than for uncomplicated varicella and inpatient costs were 72% greater. Conclusion(s): Complicated varicella has a substantial health and economic burden. These data together with data on impact on quality of life are important in informing the cost-effectiveness analysis of universal varicella vaccination. Copyright ÃƒÆ’Ã¢â‚¬Å¡Ãƒâ€šÃ‚Â© 2019 European Centre for Disease Prevention and Control (ECDC). All rights reserved.</t>
   </si>
   <si>
-    <t>The article discusses economic burden but does not explicitly mention cash-releasing savings or positive ROI.</t>
-  </si>
-  <si>
     <t>Background The WHO recognises several specialist rehabilitation provision models; in-patient, outpatient and outreach. Intensive early neurorehabilitation is required after severe Acquired Brain Injury (ABI), usually necessitating in-patient care. In the UK, children receiving specialist neurorehabilitation often remain in-patients for long periods because of the lack of appropriate out-of-hospital provision. Aims To explore feasibility and funding implications of developing a regional specialist neurorehabilitation outreach service to facilitate earlier discharge. Methods Analysis of data on children receiving in-patient neurorehabilitation at a paediatric Regional Neuroscience Centre (RNSC), 2014-2018. Information concerning therapy provision was obtained from Trust Clinical Information System Suite (CISS). Patient dependency and rehabilitation complexity was assessed by Rehabilitation Complexity Scale-Extended (RCS-E), scored by multi-disciplinary team (MDT) at weekly meetings over 15 months. For modelling purposes, a specialist neurorehabilitation outreach tariff equating to 50% in-patient tariff was assumed. Data analysis was undertaken by linear programming model (XpressIveÃƒÆ’Ã¢â‚¬Å¡Ãƒâ€šÃ‚Â©) and Discrete-Even Simulation (Simul8 ÃƒÆ’Ã¢â‚¬Å¡Ãƒâ€šÃ‚Â©).Various eligibility criteria for outreach provision were modelled: 1) needing &gt;=1 therapies&lt;3 times/week; 2) Total RCS-E score &lt;9,&lt;11 or&lt;13; 3) Therapy Dependency (TD) +Therapy Intensity (TI) components of RCS-E &lt;5. Results 156 children received neurorehabilitation as in-patients over 4 years. Mean age=7.34 years (range 0.1-17). 66 (55%) were male, 53 (45%) female. 84% had ABI, others acquired spinal injury, acute polyneuropathy or somatisation disorders. 52% lived &gt;40 miles from RNSC, 47%&gt;60 min' drive away. 49% were inpatients 1-28 days; 34%, 29-84 days; 18, 85-168 days; 6,&gt;168 days. Patients showed significant functional improvements between admission to neurorehabilitation and discharge (p&lt;0.001). Modelling suggests 14 outreach centres, including RNSC, would be required to permit 78% patients to access specialist neurorehabilitation &lt;30 mins drive from home; 10 centres would permit 92% to access neurorehabilitation &lt;45 min' drive away; 8 centres would permit 96% to access neurorehabilitation &lt;60 min' drive away. Calculations assuming outreach tariff=50% in-patient tariff, and various RCS data models, suggest annual cost savings ranging from 53,424-166,950; calculations based on CISS data, suggest average savings of 1 05 596 per year (range 98,500-113,526). Conclusion Modelling supports the feasibility and affordability of specialist neurorehabilitation outreach provision, although efficacy remains uncertain.</t>
   </si>
   <si>
@@ -877,36 +871,15 @@
     <t>- Background Randomized controlled trials (RCTs) have yielded conflicting results regarding the ability of betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers to influence perioperative cardiovascular morbidity and mortality. Thus routine prescription of these drugs in unselected patients remains a controversial issue. A previous version of this review assessing the effectiveness of perioperative betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers in cardiac and nonÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcardiac surgery was last published in 2018. The previous review has now been split into two reviews according to type of surgery. This is an update and assesses the evidence in cardiac surgery only. Objectives To assess the effectiveness of perioperatively administered betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers for the prevention of surgeryÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Ârelated mortality and morbidity in adults undergoing cardiac surgery. Search methods We searched CENTRAL, MEDLINE, Embase, CINAHL, Biosis Previews and Conference Proceedings Citation IndexÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂScience on 28 June 2019. We searched clinical trials registers and grey literature, and conducted backwardÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â and forwardÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcitation searching of relevant articles. Selection criteria We included RCTs and quasiÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Ârandomized studies comparing betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers with a control (placebo or standard care) administered during the perioperative period to adults undergoing cardiac surgery. We excluded studies in which all participants in the standard care control group were given a pharmacological agent that was not given to participants in the intervention group, studies in which all participants in the control group were given a betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblocker, and studies in which betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers were given with an additional agent (e.g. magnesium). We excluded studies that did not measure or report review outcomes. Data collection and analysis Two review authors independently assessed studies for inclusion, extracted data, and assessed risks of bias. We assessed the certainty of evidence with GRADE. Main results We included 63 studies with 7768 participants; six studies were quasiÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Ârandomized and the remaining were RCTs. All participants were undergoing cardiac surgery, and in most studies, at least some of the participants were previously taking betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers. Types of betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers were: propranolol, metoprolol, sotalol, esmolol, landiolol, acebutolol, timolol, carvedilol, nadolol, and atenolol. In twelve studies, betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers were titrated according to heart rate or blood pressure. Duration of administration varied between studies, as did the time at which drugs were administered; in nine studies this was before surgery, in 20 studies during surgery, and in the remaining studies betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers were started postoperatively. Overall, we found that most studies did not report sufficient details for us to adequately assess risk of bias. In particular, few studies reported methods used to randomize participants to groups. In some studies, participants in the control group were given betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers as rescue therapy during the study period, and all studies in which the control was standard care were at high risk of performance bias because of the openÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âlabel study design. No studies were prospectively registered with clinical trials registers, which limited the assessment of reporting bias. We judged 68% studies to be at high risk of bias in at least one domain. Study authors reported few deaths (7 per 1000 in both the intervention and control groups), and we found lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence that betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers may make little or no difference to allÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcause mortality at 30 days (risk ratio (RR) 0.95, 95% confidence interval (CI) 0.47 to 1.90; 29 studies, 4099 participants). For myocardial infarctions, we found no evidence of a difference in events (RR 1.05, 95% CI 0.72 to 1.52; 25 studies, 3946 participants; lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). Few study authors reported cerebrovascular events, and the evidence was uncertain (RR 1.37, 95% CI 0.51 to 3.67; 5 studies, 1471 participants; very lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). Based on a control risk of 54 per 1000, we found lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence that betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers may reduce episodes of ventr cular arrhythmias by 32 episodes per 1000 (RR 0.40, 95% CI 0.25 to 0.63; 12 studies, 2296 participants). For atrial fibrillation or flutter, there may be 163 fewer incidences with betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers, based on a control risk of 327 incidences per 1000 (RR 0.50, 95% CI 0.42 to 0.59; 40 studies, 5650 participants; lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). However, the evidence for bradycardia and hypotension was less certain. We found that betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers may make little or no difference to bradycardia (RR 1.63, 95% CI 0.92 to 2.91; 12 studies, 1640 participants; lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence), or hypotension (RR 1.84, 95% CI 0.89 to 3.80; 10 studies, 1538 participants; lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). We used GRADE to downgrade the certainty of evidence. Owing to studies at high risk of bias in at least one domain, we downgraded each outcome for study limitations. Based on effect size calculations in the previous review, we found an insufficient number of participants in all outcomes (except atrial fibrillation) and, for some outcomes, we noted a wide confidence interval; therefore, we also downgraded outcomes owing to imprecision. The evidence for atrial fibrillation and length of hospital stay had a moderate level of statistical heterogeneity which we could not explain, and we, therefore, downgraded these outcomes for inconsistency. Authors' conclusions We found no evidence of a difference in early allÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcause mortality, myocardial infarction, cerebrovascular events, hypotension and bradycardia. However, there may be a reduction in atrial fibrillation and ventricular arrhythmias when betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers are used. A larger sample size is likely to increase the certainty of this evidence. Four studies awaiting classification may alter the conclusions of this review. Plain language summary BetaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers to prevent death or serious events after heart surgery This review assessed evidence of whether betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers given around the time of surgery can reduce death or other serious events for people undergoing heart surgery. Background People undergoing heart surgery are at greater risk of complications and death. Heart surgery increases the amount of stress in the body, causing the release of the hormones adrenaline and noradrenaline. This stress can lead to serious events including death, heart attacks, stroke, or an irregular heartbeat. BetaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers are drugs that block the action of adrenaline and noradrenaline on the heart. BetaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers can slow down the heart and reduce blood pressure, and this effect may reduce the risk of serious events. However, they can also lead to a very low heart rate or very low blood pressure, and this effect may increase the risk of death or a stroke. Prevention of complications around the time of surgery is an important safety consideration for people undergoing heart surgery. Study characteristics The evidence is current to 28 June 2019. We included 63 studies with 7768 adults who were undergoing heart surgery, including coronary artery bypass graft and valve replacement surgery. Studies were mostly randomized controlled studies, and six were quasiÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Ârandomized (participants were allocated to groups by methods such as using hospital record numbers or dates of birth). The types of betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers were: propranolol, metoprolol, sotalol, esmolol, landiolol, acebutolol, timolol, carvedilol, nadolol, and atenolol. These betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers were compared with either a placebo (disguised to look like a betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblocker but containing no medicine) or with standard care. BetaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers were started before surgery, during surgery or at the latest by the end of the first day after surgery. The length of time betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers were given varied between studies. In most studies, at least some of the people were already taking betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers, which would be expected for people who had conditions that needed heart surgery. Key results BetaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers probably make little or no difference to the number of people who die (29 studies, 4099 participants) or have a heart attack (25 studies, 3946 participants) within 30 days of surgery. This w s supported by lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence. Few studies reported on people who had a stroke, and we were uncertain whether or not betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers reduced strokes because the certainty of the evidence was very low (5 studies, 1471 participants). BetaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers may reduce atrial fibrillation, which is an irregular heartbeat starting in the atrial chambers of the heart that increases the risk of stroke if untreated (40 studies, 5650 participants; lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). BetaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers may also reduce ventricular arrhythmias, which are potentially lifeÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âthreatening irregular heartbeat rhythms originating in the main chambers of the heart, and which may need immediate medical treatment (12 studies, 2296 participants). We found that betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers may make little or no difference to whether people experience a very low heart rate or very low blood pressure. We were uncertain whether betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers made a difference to the number of deaths up to a year after surgery (3 studies, 511 participants), to death because of the heart (4 studies, 320 participants), or to people who had heart failure (3 studies, 311 participants). The certainty of this evidence was very low. People who took betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers had a shorter hospital stay by about half a day (14 studies, 2450 participants; lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). No studies assessed whether people on betaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers had a better quality of life after heart surgery. Certainty of the evidence The certainty of the evidence in this review was mostly low. We found that many studies reported methods that we believed could influence the results. For example, many studies did not use a placeboÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcontrol and the doctors might, therefore, have treated people differently in each group. We were unable to explain some of the differences that we found in the data for atrial fibrillation. We also needed to have evidence from a larger number of participants to be very confident in our findings. Conclusion BetaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers may be beneficial for people who are undergoing cardiac surgery because they may reduce the number of people who experience atrial fibrillation and ventricular arrhythmias. BetaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âblockers may make little or no difference to the other outcomes in this review, including death, heart attacks or stroke.</t>
   </si>
   <si>
-    <t>The article focuses on clinical outcomes without explicit mention of cash-releasing savings.</t>
-  </si>
-  <si>
-    <t>The article does not mention explicit cash-releasing savings or positive ROI.</t>
-  </si>
-  <si>
     <t>Introduction - Abdominal aortic aneurysm (AAA) screening programmes have been established for men in several countries. Whether screening should be extended to women is uncertain. The objective of this study was to evaluate the cost-effectiveness of population screening for AAA in women, and compare a range of screening options. Methods - A discrete event simulation model was developed to provide a clinically realistic model of screening, surveillance, and elective and emergency AAA repair in women. Input parameters specifically for women were obtained from surgical registries, published literature and national administrative datasets. Screening was modelled for women aged 65 years or over. The model was run for 10-million women, with parameter uncertainty addressed by probabilistic and deterministic sensitivity analyses. UK costs in pounds sterling were converted to Euros based on 2016 average OECD purchasing power parity. Results - The prevalence of AAA (aortic diameter 33.0cm) was estimated as 0.43% in women aged 65 years and 1.15% at age 75. The corresponding attendance rates following invitation to screening were estimated as 73% and 62%. The base-case model adopted the same age at screening (65 years), definition of AAA (33.0cm), surveillance intervals (1 year for 3.0-4.4cm AAAs, 3 months for 4.5-5.4cm) and AAA diameter for consideration of surgery (5.5cm) as in the UK NHS AAA screening programmes. For screening at age 65, per woman invited to screening, the estimated gain in QALYs was 0.00075 (just under one day of life per woman screened), and the incremental cost was 33.51 (36.33) (all values discounted). This gave an incremental cost-effectiveness ratio (ICER) of 45,000 (48,782) per quality-adjusted life-year (QALY) gained (current UK threshold for implementation approximately 20,000 (21,681)). Under the base-case model around 2800 women would need to be invited to screening to prevent one death from AAA and screening would cost 100,000 (108,406) per death from AAA prevented (non-discounted). Sensitivity analyses did not bring the ICER below 20,000 per QALY gained, with the exception of doubling the AAA prevalence to 0.86% where the ICER was 18,000 (19,513). Alternative screening options (increasing the screening age to 70 years, lowering the threshold for considering surgery to 5.0 or 4.5cm, lowering the diameter defining an AAA in women to 2.5cm, and lengthening the surveillance intervals for the smallest AAAs) did not bring the ICER below 30,000 (32,522) per QALY gained when considered either singly or in combination. Conclusion - The current UK cost-effectiveness criteria for a population-based AAA screening programme in women are not currently met. Copyright ÃƒÆ’Ã¢â‚¬Å¡Ãƒâ€šÃ‚Â© 2019</t>
   </si>
   <si>
-    <t>The article only reports cost-effectiveness (ICER/QALY) without explicit savings.</t>
-  </si>
-  <si>
-    <t>The article focuses on cost-effectiveness and health outcomes without explicit cash-releasing savings.</t>
-  </si>
-  <si>
-    <t>The article reports cost-effectiveness and ROI without explicit cash-releasing savings.</t>
-  </si>
-  <si>
-    <t>The article reports incremental cost saving but does not explicitly mention cash-releasing savings or net savings.</t>
-  </si>
-  <si>
     <t>The article reports a clear expenditure reduction of 53,000/100 patients.</t>
   </si>
   <si>
     <t>['expenditure reduction']</t>
   </si>
   <si>
-    <t>The article only reports cost-effectiveness (ICER/QALY) without explicit cash-releasing savings.</t>
-  </si>
-  <si>
     <t>Neutropenic sepsis can be life threatening, with mortality 2-21%. The heterogeneity of patients referred with suspected neutropenic sepsis" has led to strategies being developed to risk-stratify patients and identify those with a low risk of septic complications that could be managed in the outpatient setting, such as The Multinational Association for Supportive Care in Cancer score (MASCC). Outcomes for patients referred with suspected neutropenic sepsis were assessed before and after use of MASCC guided early-supported discharge. 50/123 (41%) patients over 24 months were eligible for early-supported discharge. 26/50 patients had same-day discharge, 14 had overnight admission, 8 stayed 2 nights and 2 stayed 3 nights. Patients received on average 2 follow-up telephone consultations. There were 5 readmissions (10%) and no adverse events. In comparison group; 8 patients over 3-months would have been suitable, potentially saving 40 bed-days. This shows MASCC guided early-supported discharge is safe and cost-effective. Copyright ÃƒÆ’Ã¢â‚¬Å¡Ãƒâ€šÃ‚Â© 2019 Rila Publications Ltd."</t>
   </si>
   <si>
@@ -925,42 +898,21 @@
     <t>The article does not demonstrate explicit cash-releasing savings or positive ROI.</t>
   </si>
   <si>
-    <t>The article discusses cost-effectiveness and QALYs without explicit cash-releasing savings.</t>
-  </si>
-  <si>
-    <t>The article only reports cost-effectiveness without explicit cash-releasing savings.</t>
-  </si>
-  <si>
-    <t>The article focuses on clinical outcomes and effectiveness without explicit mention of cash-releasing savings.</t>
-  </si>
-  <si>
     <t>Aims: To develop a novel interactive budget impact model that assesses affordability of diabetes treatments in specific populations, and to test the model in a hypothetical scenario by estimating cost savings resulting from reduction in HbA&lt;inf&gt;1c&lt;/inf&gt; from &gt;=69 mmol/mol (8.5%) to a target of 53 mmol/mol (7.0%) in adults with Type 1 diabetes in the UK. Method(s): A dynamic, interactive model was created using the projected incidence and progression over a 5-year horizon of diabetes-related complications (micro- and macrovascular disease, severe hypoglycaemia and diabetic ketoacidosis) for different HbA&lt;inf&gt;1c&lt;/inf&gt; levels, with flexible input of population size, complications and therapy costs, HbA&lt;inf&gt;1c&lt;/inf&gt; distribution and other variables. The model took a National Health Service and societal perspective. Result(s): The model was developed, and in the proposed hypothetical situation, reductions in complications and expected costs evaluated. Achievement of target HbA&lt;inf&gt;1c&lt;/inf&gt; in individuals with HbA&lt;inf&gt;1c&lt;/inf&gt; &gt;=69 mmol/mol (8.5%) would reduce expected chronic complications from 6.8 to 1.2 events per 100 person-years, and diabetic ketoacidosis from 14.5 to 1.0 events per 100 person-years. Potential cumulative direct cost savings achievable in the modelled population were estimated at 687 m over 5 years (5,585/person), with total (direct and indirect) savings of 1,034 m (8,400/person). Conclusion(s): Implementation of strategies aimed at achieving target glucose levels in people with Type 1 diabetes in the UK has the potential to drive a significant reduction in complication costs. This estimate may provide insights into the potential for investment in achieving savings through improved diabetes care in the UK. Copyright ÃƒÆ’Ã¢â‚¬Å¡Ãƒâ€šÃ‚Â© 2019 Diabetes UK</t>
   </si>
   <si>
-    <t>The article discusses potential cost savings but does not explicitly mention cash-releasing savings or net savings.</t>
-  </si>
-  <si>
     <t>Objective: Assess the potential of hospital-wide routine screening by determining the prevalence and incidence of carbapenemase-producing organisms (CPOs) isolated from rectal screens at Barnet and Chase Farm Hospitals. Method(s): 3,553 samples were collected between 01/12/2018 and 31/08/2019: from adult critical care wards (universal screening - admission, discharge and weekly), from medical wards with risk-factor based screening according to the prevailing Public Health England (PHE) carbapenemase-producing Enterobacteriaceae (CPE) screening guidelines, or on an ad hoc basis. Prevalence was defined as previously documented positive CPO colonisation, or new positive status, as a proportion of all eligible samples. Incidence was defined as all newly positive patients per 1,000 patient-days. Result(s): Overall CPO prevalence was 2.1% (95% CI: 1.61-2.58%). Inpatient prevalence was significantly higher at 2.6% vs outpatient at 0.5% (p &lt; 0.001). Incidence was 0.44 per 1,000 patient-days (95% CI: 0.33-0.57), with a rate ratio between Barnet and Chase Farm of 4.9 (p = 0.013). Incidence was highest where universal screening strategy was applied (3.9 per 1000 patient-days, 95% CI: 2.4-5.91). This was 2.5 times higher than risk-factor based screening (p = 0.005) and 23.5 times that of wards without routine surveillance implemented (p &lt; 0.001). Conclusion(s): Surveillance remains a cornerstone in controlling CPO transmission. Our local incidence, lacking hospital-wide screening, significantly exceeded the reported UK average. Universal screening could help to uncover the true prevalence and incidence of CPO, thereby providing the necessary information to properly control transmission, reducing nosocomial outbreaks and ultimately reducing the overall cost to healthcare. Copyright ÃƒÆ’Ã¢â‚¬Å¡Ãƒâ€šÃ‚Â© 2021 The Authors</t>
   </si>
   <si>
-    <t>The article discusses potential cost reduction but does not explicitly demonstrate cash-releasing savings.</t>
-  </si>
-  <si>
     <t>The article states that surveillance would be cost-saving within the NHS.</t>
   </si>
   <si>
-    <t>['cost-saving']</t>
-  </si>
-  <si>
     <t>Antiemetics for adults for prevention of nausea and vomiting caused by moderately or highly emetogenic chemotherapy: a network metaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âanalysis</t>
   </si>
   <si>
     <t>- Background About 70% to 80% of adults with cancer experience chemotherapyÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âinduced nausea and vomiting (CINV). CINV remains one of the most distressing symptoms associated with cancer therapy and is associated with decreased adherence to chemotherapy. Combining 5ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂhydroxytryptamineÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â3 (5ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂHTÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€ Ã¢â‚¬â„¢) receptor antagonists with corticosteroids or additionally with neurokininÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â1 (NKÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€šÃ‚Â) receptor antagonists is effective in preventing CINV among adults receiving highly emetogenic chemotherapy (HEC) or moderately emetogenic chemotherapy (MEC). Various treatment options are available, but direct headÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂtoÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âhead comparisons do not allow comparison of all treatments versus another. Objectives ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¢ In adults with solid cancer or haematological malignancy receiving HEC ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â To compare the effects of antiemetic treatment combinations including NKÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€šÃ‚Â receptor antagonists, 5ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂHTÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€ Ã¢â‚¬â„¢ receptor antagonists, and corticosteroids on prevention of acute phase (Day 1), delayed phase (Days 2 to 5), and overall (Days 1 to 5) chemotherapyÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âinduced nausea and vomiting in network metaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âanalysis (NMA) ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â To generate a clinically meaningful treatment ranking according to treatment safety and efficacy ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¢ In adults with solid cancer or haematological malignancy receiving MEC ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â To compare whether antiemetic treatment combinations including NKÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€šÃ‚Â receptor antagonists, 5ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂHTÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€ Ã¢â‚¬â„¢ receptor antagonists, and corticosteroids are superior for prevention of acute phase (Day 1), delayed phase (Days 2 to 5), and overall (Days 1 to 5) chemotherapyÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âinduced nausea and vomiting to treatment combinations including 5ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂHTÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€ Ã¢â‚¬â„¢ receptor antagonists and corticosteroids solely, in network metaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âanalysis ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â To generate a clinically meaningful treatment ranking according to treatment safety and efficacy Search methods We searched CENTRAL, MEDLINE, Embase, conference proceedings, and study registries from 1988 to February 2021 for randomised controlled trials (RCTs). Selection criteria We included RCTs including adults with any cancer receiving HEC or MEC (according to the latest definition) and comparing combination therapies of NKÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€šÃ‚Â and 5ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂHTÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€ Ã¢â‚¬â„¢ inhibitors and corticosteroids for prevention of CINV. Data collection and analysis We used standard methodological procedures expected by Cochrane. We expressed treatment effects as risk ratios (RRs). Prioritised outcomes were complete control of vomiting during delayed and overall phases, complete control of nausea during the overall phase, quality of life, serious adverse events (SAEs), and onÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âstudy mortality. We assessed GRADE and developed 12 'Summary of findings' tables. We report results of most crucial outcomes in the abstract, that is, complete control of vomiting during the overall phase and SAEs. For a comprehensive illustration of results, we randomly chose aprepitant plus granisetron as exemplary reference treatment for HEC, and granisetron as exemplary reference treatment for MEC. Main results Highly emetogenic chemotherapy ( HEC) We included 73 studies reporting on 25,275 participants and comparing 14 treatment combinations with NKÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€šÃ‚Â and 5ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂHTÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€ Ã¢â‚¬â„¢ inhibitors. All treatment combinations included corticosteroids. Complete control of vomiting during the overall phase We estimated that 704 of 1000 participants achieve complete control of vomiting in the overall treatment phase (one to five days) when treated with aprepitant + granisetron. Evidence from NMA (39 RCTs, 21,642 participants; 12 treatment combinations with NKÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€šÃ‚Â and 5ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂHTÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€ Ã¢â‚¬â„¢ inhibitors) suggests that the following drug combinations are more efficacious than aprepitant + granisetron for completely controlling vomiting during the overall treatment phase (one to five days): fosnetupitant + palonosetron (810 of 1000; RR 1.15, 95% confidence interval (CI) 0.97 to 1.37; moderate certainty), aprepitant + palonosetron (753 of 1000; RR 1.07, 95% CI 1.98 to 1.18; lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty), aprepitant + ramosetron (753 of 1000; RR 1.07, 95% CI 0.95 to 1.21; low certainty), and fosaprepitant + palonosetron (746 of 1000; RR 1.06, 95% CI 0.96 to .19; low certainty). Netupitant + palonosetron (704 of 1000; RR 1.00, 95% CI 0.93 to 1.08; highÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty) and fosaprepitant + granisetron (697 of 1000; RR 0.99, 95% CI 0.93 to 1.06; highÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty) have little to no impact on complete control of vomiting during the overall treatment phase (one to five days) when compared to aprepitant + granisetron, respectively. Evidence further suggests that the following drug combinations are less efficacious than aprepitant + granisetron in completely controlling vomiting during the overall treatment phase (one to five days) (ordered by decreasing efficacy): aprepitant + ondansetron (676 of 1000; RR 0.96, 95% CI 0.88 to 1.05; low certainty), fosaprepitant + ondansetron (662 of 1000; RR 0.94, 95% CI 0.85 to 1.04; low certainty), casopitant + ondansetron (634 of 1000; RR 0.90, 95% CI 0.79 to 1.03; low certainty), rolapitant + granisetron (627 of 1000; RR 0.89, 95% CI 0.78 to 1.01; moderate certainty), and rolapitant + ondansetron (598 of 1000; RR 0.85, 95% CI 0.65 to 1.12; low certainty). We could not include two treatment combinations (ezlopitant + granisetron, aprepitant + tropisetron) in NMA for this outcome because of missing direct comparisons. Serious adverse events We estimated that 35 of 1000 participants experience any SAEs when treated with aprepitant + granisetron. Evidence from NMA (23 RCTs, 16,065 participants; 11 treatment combinations) suggests that fewer participants may experience SAEs when treated with the following drug combinations than with aprepitant + granisetron: fosaprepitant + ondansetron (8 of 1000; RR 0.23, 95% CI 0.05 to 1.07; low certainty), casopitant + ondansetron (8 of 1000; RR 0.24, 95% CI 0.04 to 1.39; low certainty), netupitant + palonosetron (9 of 1000; RR 0.27, 95% CI 0.05 to 1.58; low certainty), fosaprepitant + granisetron (13 of 1000; RR 0.37, 95% CI 0.09 to 1.50; low certainty), and rolapitant + granisetron (20 of 1000; RR 0.57, 95% CI 0.19 to 1.70; low certainty). Evidence is very uncertain about the effects of aprepitant + ondansetron (8 of 1000; RR 0.22, 95% CI 0.04 to 1.14; very low certainty), aprepitant + ramosetron (11 of 1000; RR 0.31, 95% CI 0.05 to 1.90; very low certainty), fosaprepitant + palonosetron (12 of 1000; RR 0.35, 95% CI 0.04 to 2.95; very low certainty), fosnetupitant + palonosetron (13 of 1000; RR 0.36, 95% CI 0.06 to 2.16; very low certainty), and aprepitant + palonosetron (17 of 1000; RR 0.48, 95% CI 0.05 to 4.78; very low certainty) on the risk of SAEs when compared to aprepitant + granisetron, respectively. We could not include three treatment combinations (ezlopitant + granisetron, aprepitant + tropisetron, rolapitant + ondansetron) in NMA for this outcome because of missing direct comparisons. Moderately emetogenic chemotherapy (MEC) We included 38 studies reporting on 12,038 participants and comparing 15 treatment combinations with NKÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€šÃ‚Â and 5ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂHTÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€ Ã¢â‚¬â„¢ inhibitors, or 5ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂHTÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€ Ã¢â‚¬â„¢ inhibitors solely. All treatment combinations included corticosteroids. Complete control of vomiting during the overall phase We estimated that 555 of 1000 participants achieve complete control of vomiting in the overall treatment phase (one to five days) when treated with granisetron. Evidence from NMA (22 RCTs, 7800 participants; 11 treatment combinations) suggests that the following drug combinations are more efficacious than granisetron in completely controlling vomiting during the overall treatment phase (one to five days): aprepitant + palonosetron (716 of 1000; RR 1.29, 95% CI 1.00 to 1.66; low certainty), netupitant + palonosetron (694 of 1000; RR 1.25, 95% CI 0.92 to 1.70; low certainty), and rolapitant + granisetron (660 of 1000; RR 1.19, 95% CI 1.06 to 1.33; high certainty). Palonosetron (588 of 1000; RR 1.06, 95% CI 0.85 to 1.32; low certainty) and aprepitant + granisetron (577 of 1000; RR 1.06, 95% CI 0.85 to 1.32; low certainty) may or may not increase complete response in the overall treatment phase (one to five days) when compared to granisetron, respectively. Azasetron (560 of 1000; RR 1.01, 95% CI 0.76 to 1.34; low certainty) may result in little to no difference in complete response in the overall treatment phase (one to five days) when compared to granisetron. Evidence further suggests that the following drug combinations are less efficacious than granisetron in completely controlling vomiting during the overall treatment phase (one to five days) (ordered by decreasing efficacy): fosaprepitant + ondansetron (500 of 1000; RR 0.90, 95% CI 0.66 to 1.22; low certainty), aprepitant + ondansetron (477 of 1000; RR 0.86, 95% CI 0.64 to 1.17; low certainty), casopitant + ondansetron (461 of 1000; RR 0.83, 95% CI 0.62 to 1.12; low certainty), and ondansetron (433 of 1000; RR 0.78, 95% CI 0.59 to 1.04; low certainty). We could not include five treatment combinations (fosaprepitant + granisetron, azasetron, dolasetron, ramosetron, tropisetron) in NMA for this outcome because of missing direct comparisons. Serious adverse events We estimated that 153 of 1000 participants experience any SAEs when treated with granisetron. Evidence from pairÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âwise comparison (1 RCT, 1344 participants) suggests that more participants may experience SAEs when treated with rolapitant + granisetron (176 of 1000; RR 1.15, 95% CI 0.88 to 1.50; low certainty). NMA was not feasible for this outcome because of missing direct comparisons. Certainty of evidence Our main reason for downgrading was serious or very serious imprecision (e.g. due to wide 95% CIs crossing or including unity, few events leading to wide 95% CIs, or small information size). Additional reasons for downgrading some comparisons or whole networks were serious study limitations due to high risk of bias or moderate inconsistency within networks. Authors' conclusions This field of supportive cancer care is very well researched. However, new drugs or drug combinations are continuously emerging and need to be systematically researched and assessed. For people receiving HEC, synthesised evidence does not suggest one superior treatment for prevention and control of chemotherapyÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âinduced nausea and vomiting. For people receiving MEC, synthesised evidence does not suggest superiority for treatments including both NKÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€šÃ‚Â and 5ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂHTÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€ Ã¢â‚¬â„¢ inhibitors when compared to treatments including 5ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂHTÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€ Ã¢â‚¬â„¢ inhibitors only. Rather, the results of our NMA suggest that the choice of 5ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂHTÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã…Â¡Ãƒâ€ Ã¢â‚¬â„¢ inhibitor may have an impact on treatment efficacy in preventing CINV. When interpreting the results of this systematic review, it is important for the reader to understand that NMAs are no substitute for direct headÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂtoÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âhead comparisons, and that results of our NMA do not necessarily rule out differences that could be clinically relevant for some individuals. Plain language summary Which drug combinations are best for prevention of nausea and vomiting caused by chemotherapy in adults with cancer? The burden of nausea and vomiting caused by chemotherapy and what helps to prevent it? In about 70% to 80% of adults with cancer, chemotherapy induces nausea and vomiting (CINV). Depending on the type of chemotherapy, treatment can cause strong or moderate sickness (hereafter referred to as HEC (highly emetogenic chemotherapy) and MEC (moderately emetogenic chemotherapy)). Multiple drug combinations have showed high benefit for CINV among adults receiving HEC or MEC. What was the aim of our review? Using a network metaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âanalysis, we aimed to compare the benefits and harms of different drug combinations for prevention of CINV among people receiving HEC or MEC, and to identify treatment ranking. A network metaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âanalysis is a technique used to compare different treatments described in already published trials, even when the original individual trial does not describe such comparisons. What studies did we look at? We searched selected medical databases and trial registries until February 2021. We included studies comparing multiple drug combinations for prevention of CINV among adults with any type of cancer receiving HEC or MEC that is commonly used in clinical practice. In particular, we looked at drugs inhibiting two specific biochemical receptors (neurokinin receptor and serotonin receptor) that trigger nausea and vomiting after chemotherapy. We looked at the preventative effects of these treatments over five days. This is the period during which the maximum intensity of CINV and further peaks of intensity are expected, after the start of chemotherapy. Our key results... ...for people receiving HEC We found 73 studies that reported on the experience of 25,275 participants and compared 14 treatment combinations of our interest. Benefits. Over five days, investigated treatments helped to prevent any vomiting in 60% to 81% of people on average. Those individuals also had no need for rescue medicines, which are used in case nausea and vomiting occur even though prophylactic treatment has been given. The results of our analysis suggest some differences in effectiveness of different treatments, but overall we had little confidence that those differences would be reflected in realÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âworld observations. Harms. We estimated that 1% to 4% of people experience serious side effects. The differences between treatments were small. ...for people receiving MEC We found 38 studies that reported on the experience of 12,038 participants and compared 15 treatment combinations of our interest. Benefits. Over five days, investigated treatments helped prevent any vomiting in 43% to 72% of people on average. Those individuals also had no need for rescue medicines. The results of our analysis suggest some differences in the effectiveness of different treatments, but overall, we had little confidence that those differences would be reflected in realÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âworld observations. Harms. Few studies reported serious side effects. The ones that did suggest that on average 15% to 18% of people experience such events. Differences between treatments were small. However, we think that future research is needed to rule out potential differences between treatments. Our confidence in the findings We assessed how confident we were that there are differences between compared treatments. We had low or very low confidence that one treatment is better or worse than another in preventing CINV. Our confidence in differences between statistical results was mainly limited because measures of variation were wide apart and included both potential advantages and disadvantages, although measures of precision showed no or little effect. We also identified limitations in some of the included studies, which further limited our confidence in the effects. This was mainly the case when study personnel and participants knew which treatments were given and therefore may not adhere to the planned intervention, or may perceive or report effects differently. Our conclusions The results of our analysis suggest that there is no superior drug combination for prevention of CINV for people receiving HEC or MEC. However, results suggest that the choice of drugs targeting the serotonin receptor may impact effectiveness, irrespective of whether given with or without a drug targeting the neurokinin receptor. However, when interpreting these results, it is important for the reader to understand that these kinds of multipleÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcomparison analyses are no substitute for headÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂtoÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âhead comparisons, and that the results do not necessarily rule out differences that could be clinically relevant for some individuals. How upÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂtoÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âdate is this evidence? Evidence is upÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂtoÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âdate to 2 February 2021.</t>
   </si>
   <si>
-    <t>The article focuses on clinical outcomes and treatment efficacy without mentioning explicit cash-releasing savings.</t>
-  </si>
-  <si>
     <t>Secondary prevention of variceal bleeding in adults with previous oesophageal variceal bleeding due to decompensated liver cirrhosis: a network metaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âanalysis</t>
   </si>
   <si>
@@ -970,15 +922,6 @@
     <t>The article focuses on clinical outcomes and does not explicitly mention cash-releasing savings or positive ROI.</t>
   </si>
   <si>
-    <t>The article discusses cost-effectiveness but does not explicitly mention cash-releasing savings or positive ROI.</t>
-  </si>
-  <si>
-    <t>No explicit cash-releasing savings or ROI mentioned.</t>
-  </si>
-  <si>
-    <t>The article explicitly mentions a cost saving of 6270, which implies a net saving.</t>
-  </si>
-  <si>
     <t>['net saving']</t>
   </si>
   <si>
@@ -991,19 +934,10 @@
     <t>The article reports an expenditure reduction from 16 million to 11 million.</t>
   </si>
   <si>
-    <t>The article reports cost reductions, indicating expenditure reduction.</t>
-  </si>
-  <si>
     <t>Background: Screening for renal cell carcinoma (RCC) has been identified as a key research priority; however, no randomised control trials have been performed. Value of information analysis can determine whether further research on this topic is of value. Objective(s): To determine (1) whether current evidence suggests that screening is potentially cost-effective and, if so, (2) in which age/sex groups, (3) identify evidence gaps, and (4) estimate the value of further research to close those gaps. Design, setting, and participants: A decision model was developed evaluating screening in asymptomatic individuals in the UK. A National Health Service perspective was adopted. Intervention(s): A single focused renal ultrasound scan compared with standard of care (no screening). Outcome measurements and statistical analysis: Expected lifetime costs, quality-adjusted life years (QALYs), and incremental cost-effectiveness ratio (ICER), discounted at 3.5% per annum. Results and limitations: Given a prevalence of RCC of 0.34% (0.18-0.54%), screening 60-yr-old men resulted in an ICER of 18 092/QALY (22 843/QALY). Given a prevalence of RCC of 0.16% (0.08-0.25%), screening 60-yr-old women resulted in an ICER of 37 327/QALY (47 129/QALY). In the one-way sensitivity analysis, the ICER was &lt;30 000/QALY as long as the prevalence of RCC was &gt;=0.25% for men and &gt;=0.2% for women at age 60 yr. Given the willingness to pay a threshold of 30 000/QALY (37 878/QALY), the population-expected values of perfect information were 194 million (244 million) and 97 million (123 million) for 60-yr-old men and women, respectively. The expected value of perfect parameter information suggests that the prevalence of RCC and stage shift associated with screening are key research priorities. Conclusion(s): Current evidence suggests that one-off screening of 60-yr-old men is potentially cost-effective and that further research into this topic would be of value to society. Patient Summary: Economic modelling suggests that screening 60-yr-old men for kidney cancer using ultrasound may be a good use of resources and that further research on this topic should be performed. Copyright ÃƒÆ’Ã¢â‚¬Å¡Ãƒâ€šÃ‚Â© 2019 European Association of Urology</t>
   </si>
   <si>
-    <t>The article reports reduced readmission costs, indicating expenditure reduction.</t>
-  </si>
-  <si>
     <t>- Rationale Postpartum haemorrhage (PPH) is common and potentially lifeÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âthreatening. The antifibrinolytic drug tranexamic acid (TXA) is thought to be effective for treating PPH. There is growing interest in whether TXA is effective for preventing PPH after vaginal birth. In randomised controlled trials (RCTs), TXA has been associated with increased risk of seizures and unexplained increased mortality when given more than three hours after traumatic bleeding. Reliable evidence on the effects, costÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âeffectiveness and safety of prophylactic TXA is required before considering widespread use. This review updates one published in 2015. Objectives To assess the effects of TXA for preventing PPH compared to placebo or no treatment (with or without uterotonic coÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âtreatment) in women following vaginal birth. Search methods We searched MEDLINE, Embase, CENTRAL, and WHO ICTRP (to 6 September 2024). We also searched reference lists of retrieved studies. Eligibility criteria We included RCTs evaluating TXA alone or in addition to standard care (uterotonics) for preventing PPH following vaginal birth. For this update, we required trials to be prospectively registered (before participant recruitment), and we applied a trustworthiness checklist. Outcomes Critical outcomes were blood loss ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã‚Â°Ãƒâ€šÃ‚Â¥ 500 mL and blood loss ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã‚Â°Ãƒâ€šÃ‚Â¥ 1000 mL. Important outcomes included maternal death, severe morbidity, blood transfusion, receipt of additional surgical interventions to control PPH, thromboembolic events, receipt of additional uterotonics, hysterectomy, and maternal satisfaction. Risk of bias We used the Cochrane risk of bias tool (RoB 1) to assess the risk of bias in the studies. Synthesis methods Two review authors independently selected trials, extracted data, assessed risk of bias, and assessed trial trustworthiness. We used randomÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âeffects metaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âanalysis to combine data. We assessed the certainty of the evidence using GRADE. Included studies We included three RCTs with 18,974 participants in total. The trials were conducted in both highÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â and lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âresource settings and involved participants at both low and high risk of PPH. The trials compared intravenous TXA (1 g) and standard care versus placebo (saline) and standard care. After applying our trustworthiness checklist, we did not include any of the 12 trials in the previous version of this review. Synthesis of results Prophylactic tranexamic acid in addition to standard care compared to placebo in addition to standard care TXA results in little to no difference in blood loss ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã‚Â°Ãƒâ€šÃ‚Â¥ 500 mL (risk ratio (RR) 0.93, 95% confidence interval (CI) 0.81 to 1.06; 2 studies, 18,897 participants; 5 fewer per 1000, 95% CI 15 fewer to 5 more; highÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). TXA likely results in little to no difference in blood loss ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã‚Â°Ãƒâ€šÃ‚Â¥ 1000 mL (RR 0.86, 95% CI 0.69 to 1.07; 2 studies, 18,897 participants; 3 fewer per 1000, 95% CI 6 fewer to 1 more; moderateÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). TXA likely results in little to no difference in severe morbidity (RR 0.88, 95% CI 0.69 to 1.12; 1 study, 15,066 participants; 2 fewer per 1000, 95% CI 6 fewer to 2 more; moderateÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). TXA results in little to no difference in receipt of blood transfusion (RR 1.00, 95% CI 0.95 to 1.06; 3 studies, 18,972 participants; 0 fewer per 1000, 95% CI 10 fewer to 12 more; highÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). TXA may result in little to no difference in receipt of additional surgical interventions to control PPH (RR 0.63, 95% CI 0.32 to 1.23; 2 studies, 18,972 participants; 1 fewer per 1000, 95% CI 2 fewer to 1 more; lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). In women with anaemia, TXA results in little to no difference in receipt of additional uterotonics (RR 1.02, 95% CI 0.94 to 1.10; 1 study, 15,066 participants; 3 more women per 1000, 95% CI 8 fewer to 24 more; highÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). In women with no anaemia, TXA results in a slight reduction in receipt of additional uterotonics (RR 0.75, 95% CI 0.61 to 0.92; 1 study, 3891 participants; 24 fewer women per 1000, 95% CI 38 fewer to 8 fewer; highÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). TXA likely r sults in little to no difference in maternal satisfaction. The evidence is very uncertain about the effect of TXA on maternal death, thromboembolic events, and hysterectomy (very lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence): maternal death (RR 0.99, 95% CI 0.39 to 2.49; 2 studies, 15,081 participants; 0 fewer per 1000, 95% CI 1 fewer to 2 more); thromboembolic events (RR 0.25, 95% CI 0.03 to 2.24; 3 studies, 18,774 participants; 3 fewer women per 10,000, 95% CI 4 fewer to 5 more); hysterectomy (RR 0.89, 95% CI 0.36 to 2.19; 1 study, 15,066 participants; 1 fewer women per 10,000, 95% CI 9 fewer to 16 more). Authors' conclusions Adding prophylactic TXA to standard care of women during vaginal birth makes little to no difference to blood loss ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã‚Â°Ãƒâ€šÃ‚Â¥ 500 mL and likely makes little to no difference to blood loss ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã‚Â°Ãƒâ€šÃ‚Â¥ 1000 mL or the risk of severe morbidity, compared to placebo and standard care. TXA may result in little to no difference in additional surgical interventions to control PPH and results in little to no difference in blood transfusions. One trial found that TXA reduced the use of additional uterotonics in women without anaemia, whereas the largest trial found little to no difference in the use of additional uterotonics in women with anaemia. Although there were very few serious adverse events reported, the evidence is insufficient to draw conclusions about the effect of TXA on maternal death, thromboembolic events, hysterectomy, or seizures. TXA likely results in little to no difference in maternal satisfaction. These findings are based mainly on two large trials. In the smaller of these, less than 30% of study participants were at high risk of PPH. In the largest trial, all participants had moderate to severe anaemia. Those making decisions about routine administration of prophylactic TXA for all women having vaginal births should consider that current evidence does not show a benefit of TXA for blood loss outcomes and related morbidity, and the evidence is very uncertain about serious adverse events. Funding This review was partially funded by the World Health Organization (WHO). Registration Protocol (2009) DOI: 10.1002/14651858.CD007872ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨Original review (2010) DOI: 10.1002/14651858.CD007872.pub2ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨Review update (2015) DOI: 10.1002/14651858.CD007872.pub3 Plain language summary What are the benefits and risks of tranexamic acid for preventing heavy bleeding after vaginal birth? Key messages Tranexamic acid given as a preventive treatment makes little to no difference to heavy bleeding after vaginal birth. We are uncertain about whether there are any harmful effects from tranexamic acid. What is the issue? Postpartum haemorrhage, which is heavy bleeding after giving birth, is a common and potentially lifeÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âthreatening complication of birthing a child. Most women receive drugs (called uterotonics) that stimulate the womb to contract after a normal (vaginal) delivery to prevent postpartum haemorrhage. Tranexamic acid (TXA) is a medication that is used to decrease blood loss in surgery and health conditions associated with increased bleeding. It works by helping to prevent the breakdown of blood clots. If a woman is bleeding heavily after birth, it decreases blood loss. We do not know if TXA can help prevent heavy bleeding after vaginal birth. What did we want to find out? We wanted to know whether fewer women have heavy bleeding after a vaginal birth if they receive TXA, with or without additional uterotonics, during vaginal birth. We also wanted to find out if taking TXA during vaginal birth was associated with any harmful effects. What did we do? We searched for and selected all the studies that addressed our question. We used a checklist to make sure we only included studies with information we could verify. We made judgements about the quality of the studies before comparing and summarising the results of the studies. Lastly, we rated our confidence in the findings. Why is this important? It is important to determine whether TXA is effective in preventing heavy bleeding after birth when given to women during vaginal birth. If there is a benefit, it could help women around the world and even play a role in reducing the number of women who die after giving birth. How up to date is this evidence? We searched for all available evidence up to 6 September 2024. What evidence did we find? We identified three studies that investigated the effects of preventive TXA. The three studies involved a total of 18,974 participants at low or high risk of heavy bleeding. Participants were given either intravenous (into a vein) TXA plus standard care or placebo (saline) injection plus standard care. We found that preventive TXA results in little to no difference in heavy bleeding after birth. We are very uncertain about the effect of TXA on maternal death. TXA likely makes no difference to the risk of women developing serious illness. We found that TXA has no effect on the likelihood of receiving a blood transfusion. TXA may result in no difference in the need for further surgical intervention after giving birth. We are very uncertain about the effect of TXA on blood clots. In women with anaemia, TXA makes no difference to the need for additional drugs to help the womb contract, but in women with no anaemia, there was a slight reduction in this outcome. We are very uncertain about the effect of TXA on hysterectomy (an operation to remove the womb). There does not seem to be a difference in maternal satisfaction. What are the limitations of the evidence? The studies included women in both highÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â and lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âresource settings. Few women experienced harmful effects. However, we cannot be certain that this is indeed the case in the real world. What does this mean? We found no difference in the number of women experiencing heavy bleeding after birth after they were given TXA preventatively during vaginal birth, and we are very uncertain about the effect of TXA on blood clots and other serious side effects. As these are harmful effects, clinicians should take into account the lack of benefit and the potential harms when considering giving routine TXA to women during vaginal birth. Further research should focus on other interventions that may help to prevent heavy bleeding after vaginal birth.</t>
-  </si>
-  <si>
-    <t>The article reports cost-effectiveness and cost savings per QALY but does not explicitly mention cash-releasing savings or net savings.</t>
   </si>
   <si>
     <t>- Background People undergoing major orthopaedic surgery are at increased risk of postoperative thromboembolic events. Low molecular weight heparins (LMWHs) are recommended for thromboprophylaxis in this population. New oral anticoagulants, including direct factor Xa inhibitors, are recommended as alternatives. They may have more advantages than disadvantages compared to LMWHs and vitamin K antagonists (VKAs, another type of anticoagulant). Objectives To assess the benefits and harms of prophylactic anticoagulation with direct factor Xa inhibitors compared with low molecular weight heparins and vitamin K antagonists in people undergoing major orthopaedic surgery for elective total hip or knee replacement or hip fracture surgery. Search methods We searched the Cochrane Vascular Specialised Register, CENTRAL, MEDLINE, Embase, two other databases, and two trial registers to 11 November 2023. We conducted reference checks to identify additional studies. Selection criteria We included randomised controlled trials (RCTs) comparing the effects of direct factor Xa inhibitors to LMWHs or VKAs in people undergoing major orthopaedic surgery. Data collection and analysis We used standard Cochrane methods. Our primary outcomes were allÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcause mortality, major venous thromboembolism (VTE), symptomatic VTE, major bleeding, and serious hepatic and nonÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âhepatic adverse events. We evaluated the risk of bias in the included studies using Cochrane's risk of bias 1 tool. We calculated estimates of treatment effects using risk ratios (RR) with 95% confidence intervals (CIs), and used GRADE criteria to assess the certainty of the evidence. Main results We included 53 RCTs (44,371 participants). Participants' average age was 64 years (range: 18 to 93 years). Only one RCT compared a VKA with direct factor Xa inhibitors. All 53 RCTs compared direct factor Xa inhibitors with LMWHs. TwentyÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âthree studies included participants undergoing total hip replacement; 21 studies, total knee replacement; and three studies included people having hip fracture surgery. The studies' average duration was approximately 42 days (range: two to 720 days). Compared to LMWHs, direct factor Xa inhibitors may have little to no effect on allÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcause mortality, but the evidence is very uncertain (RR 0.83, 95% CI 0.52 to 1.31; I 2 = 0%; 28 studies, 29,698 participants; very lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). Direct factor Xa inhibitors may make little to no difference to major venous thromboembolic events compared to LMWHs, but the evidence is very uncertain (RR 0.51, 95% CI 0.37 to 0.71; absolute risk difference: 12 fewer major VTE events per 1000 participants, 95% CI 16 fewer to 7 fewer; I 2 = 48%; 28 studies, 24,574 participants; very lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). Compared to LMWHs, direct factor Xa inhibitors may reduce symptomatic VTE (RR 0.64, 95% CI 0.50 to 0.83; I 2 = 0%; 33 studies, 31,670 participants; lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). The absolute benefit of substituting factor Xa inhibitors for LMWHs may be between two and five fewer symptomatic VTE episodes per 1000 patients. In the metaÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âanalysis with all studies pooled, direct factor Xa inhibitors appeared to make little or no difference to major bleeding compared to LMWHs, but the evidence was very uncertain (RR 1.05, 95% CI 0.86 to 1.30; I 2 = 15%; 36 studies, 39,778 participants; very low certaintyÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âevidence). ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¢ In a subgroup analysis limited to studies comparing rivaroxaban to LMWHs, people given rivaroxaban may have had more major bleeding events (RR 1.94, 95% CI 1.26 to 2.98; I 2 = 0%; 17 studies, 17,630 participants; lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). The absolute risk of substituting rivaroxaban for LMWH may be between one and seven more major bleeding events per 1000 patients. ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¢ In a subgroup analysis limited to studies comparing direct factor Xa inhibitors other than rivaroxaban to LMWHs, people given these other direct factor Xa inhibitors may have had fewer major bleeding events, but the evidence was very uncertain (RR 0.80, 95% CI 0.63 to 1.02; absolute risk difference: 3 fewer major bl eding events per 1000 participants, 95% CI 5 fewer to 0 fewer; I 2 = 0%; 19 studies, 22,148 participants; very lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). Direct factor Xa inhibitors may make little to no difference in serious hepatic adverse events compared to LMWHs, but the evidence is very uncertain (RR 3.01, 95% CI 0.12 to 73.93; 2 studies, 3169 participants; very lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). Only two studies reported this outcome, with one death in the intervention group due to hepatitis reported in one study, and no events reported in the other study. People given direct factor Xa inhibitors may have a lower risk of serious nonÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âhepatic adverse events than those given LMWHs (RR 0.89, 95% CI 0.81 to 0.97; I 2 = 18%; 15 studies, 26,246 participants; lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). The absolute benefit of substituting factor Xa inhibitors for LMWH may be between three and 14 fewer serious nonÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âhepatic adverse events per 1000 patients. Only one study compared a direct factor Xa inhibitor with a VKA. It reported outcome data with imprecise results due to the small number of events. It showed no difference in the effects of the study drugs. Authors' conclusions Oral direct factor Xa inhibitors may have little to no effect on allÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcause mortality, but the evidence is very uncertain. Oral direct factor Xa inhibitors may slightly reduce symptomatic VTE events when compared with LMWH. They may make little or no difference to major VTE events, but the evidence is very uncertain. In the evaluation of major bleeding, the evidence suggests rivaroxaban results in a slight increase in major bleeding events compared to LMWHs. The remaining oral direct factor Xa inhibitors may have little to no effect on major bleeding, but the evidence is very uncertain. Oral direct factor Xa inhibitors may reduce serious nonÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âhepatic adverse events slightly compared to LMWHs. They may have little to no effect on serious hepatic adverse events, but the evidence is very uncertain. Due to the high rates of missing participants and selective outcome reporting, the effect estimates may be biased. Plain language summary Direct factor Xa inhibitors or classic 'blood thinners': which leads to better outcomes for people undergoing major hip or knee surgery? Key messages ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¢ We do not know if classic anticoagulant medicines (commonly known as 'blood thinners') or newer bloodÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âthinning medicines called 'direct factor Xa inhibitors' (DFXa inhibitors) are better at preventing death or the development of blood clots in the deep veins of the legs or in the lungs of people who have had hip or knee replacement surgery. ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¢ Compared to classic anticoagulants, DFXa inhibitors may slightly reduce the number of people who experience blood clot symptoms (such as breathing difficulties or pain). One type of DFXa inhibitor, rivaroxaban, may slightly increase the number of people who have serious uncontrolled bleeding. Why are blood clots a concern for people having major hip or knee surgery? 'Venous thromboembolism' is when a blood clot forms in a vein, the vessels that carry blood back to the heart. Clots can narrow or block veins, leading to tissue damage, stroke, and death. People having hip or knee replacement surgery, or an operation to fix a broken hip, are at a higher risk of developing a blood clot. How can blood clots be prevented and treated? People undergoing major hip or knee surgery are typically given an anticoagulant medicine, commonly known as a 'blood thinner', to help prevent blood clots from forming. There are two main types of 'classic' anticoagulants: (1) low molecular weight heparins (LMWHs), which are injected with a needle at a fixed dose; and (2) vitamin K antagonists (VKAs), given by mouth in variable amounts. Newer anticoagulant medicines known as direct factor Xa inhibitors have been developed. They are given by mouth in fixed doses. Rivaroxaban and apixaban are types of DFXa inhibitors. What did we want to find out? We wanted to find out if DFXa inhibitors were better than classic anticoagulants at reducing the number of people who (1) died from any cause aft r major hip or knee surgery, and (2) developed blood clots or symptoms of blood clots (e.g. breathing difficulties and pain). We also wanted to find out if DFXa inhibitors were associated with any unwanted effects, including uncontrolled bleeding, serious liver disease, and other serious unwanted events. What did we do? We searched for studies that compared DFXa inhibitors with classic anticoagulants in people undergoing hip or knee surgery. We compared and summarised the results of the studies and rated our confidence in the evidence, based on factors such as study methods and sizes. What did we find? We found 53 studies that involved 44,371 adults who had hip or knee replacement surgery, and had a high risk of developing blood clots in their lungs, legs, or pelvis. They received anticoagulant treatment for 6 to 39 days, and followÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âup lasted for an average of 42 days. All 53 studies compared DFXa inhibitors with low molecular weight heparins (LMWHs). Just one study also investigated the VKA called warfarin. The biggest study involved 5407 participants, and the smallest study, 50 participants. They were conducted in countries unevenly distributed around the world; most were done in highÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âincome regions. Roughly oneÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âthird of participants (31%) were male. Participants' average age was 64 years. Pharmaceutical companies funded half of the studies (27 of 53). Main results Compared to LMWHs, we do not know if DFXa inhibitors reduce the number of people who:ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¢ die from any cause after surgery, orÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¢ develop blood clots in the lungs or deep veins of the leg or pelvisÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Â¨because the evidence is very uncertain. Compared to LMWHs, DFXa inhibitors may slightly reduce the number of people who have blood clot symptoms: between 2 and 5 fewer people out of every 1000 people given DFXa inhibitors would have blood clot symptoms compared to people given LMWHs. The DFXa inhibitor rivaroxaban may slightly increase the number of people who have major uncontrolled bleeding compared to LMWHs. Between 1 and 7 more people out of every 1000 people given rivaroxaban may have uncontrolled bleeding compared to those given LMWHs. The other DFXa inhibitors may have little to no effect on major bleeding, but the evidence is very uncertain. Compared to LMWHs, DFXa inhibitors may have little to no effect on serious unwanted events affecting the liver, but the evidence is very uncertain. They may slightly reduce other serious, nonÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂliverÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Ârelated events compared to LMWHs. Between 3 and 14 fewer people out of every 1000 people given DFXa inhibitors would have serious, nonÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂliverÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Ârelated events compared to people given LMWHs. We did not find enough studies investigating VKAs to help us answer our questions. What are the limitations of the evidence? We have little confidence in the evidence because people in some studies were aware of which treatment they were getting. Most studies did not have a complete set of results for all participants. There were insufficient studies to be certain about the results of some outcomes. How current is this evidence? The evidence is current to November 2023.</t>
@@ -1026,9 +960,6 @@
 &lt;b&gt;Funding&lt;/b&gt;: This award was funded by the National Institute for Health and Care Research (NIHR) Evidence Synthesis programme (NIHR award ref: NIHR159946) and is published in full in Health Technology Assessment; Vol. 29, No. 13. See the NIHR Funding and Awards website for further award information.</t>
   </si>
   <si>
-    <t>The article discusses potential cost-effectiveness but does not explicitly demonstrate cash-releasing savings or positive ROI.</t>
-  </si>
-  <si>
     <t>J6224</t>
   </si>
   <si>
@@ -1038,9 +969,6 @@
     <t>Background: Self-management interventions provide information and tools to people with long-term conditions to help them manage their own condition. They have been shown to improve patient outcomes and reduce healthcare utilisation. Whilst charities and healthcare providers offer information and advice, there is no effective comprehensive self-management intervention available for people in the UK living with Parkinson's. Through co-design with people with Parkinson's, carers and healthcare professionals, systematic reviews, and qualitative studies, we developed the self-management Live Well with Parkinson's toolkit, facilitated by trained supporters. The toolkit contains information about symptoms, therapies, ways to optimise wellbeing, and practical advice. There are personalised sections covering information about themselves, their health and support, a calendar, to do lists, the ability to review and track symptoms, and an asset-based wellbeing section to identify health priorities they wanted to maintain. Method(s): This toolkit was tested in a single-blind randomised controlled trial in England. Participants were community-dwelling individuals, with a diagnosis of Parkinson's and randomised 1:1 to receive the Live Well with Parkinson's toolkit or treatment as usual. The primary outcome was health-related quality of life (PDQ-39) at 12 months with a range of secondary outcome measures. Outcomes are being analysed using linear mixed models, controlling for baseline scores. Result(s): We recruited 346 participants between January 2022-July 2023 with a median age 71 years (IQR 11.25),159 (46%) women, and 297 (86%) White British. Data collection was completed in August 2024 with a retention rate of 88% at 12-month follow-up. The process evaluation revealed highly positive feedback. Clinical and cost-effectiveness analysis will be available for presentation at the conference, including primary and secondary outcomes. Conclusion(s): The outcomes of this programme will inform the effectiveness of this intervention, as well as the effective components, mechanisms, and future developments to improve quality of life for people with Parkinson's when using self-management tools. Copyright ÃƒÆ’Ã¢â‚¬Å¡Ãƒâ€šÃ‚Â© 2025</t>
   </si>
   <si>
-    <t>The article does not explicitly mention cash-releasing savings or positive ROI.</t>
-  </si>
-  <si>
     <t>J6228</t>
   </si>
   <si>
@@ -1050,9 +978,6 @@
     <t>- Rationale Despite World Health Organization (WHO) guidelines for preventing, detecting, and treating postpartum hemorrhage (PPH), effective implementation has lagged. Objectives To evaluate the clinical benefits and harms of implementation strategies used to promote adherence to WHO clinical guidelines for the prevention, detection, and treatment of PPH. Search methods We searched the Cochrane Central Register of Controlled Trials (CENTRAL), MEDLINE, Embase, CINAHL, and two trial registries, along with reference checking, citation searching, and contact with study authors. The latest search date was 25 April 2024. Eligibility criteria We included randomized controlled trials (RCTs), including cluster, pragmatic, and steppedÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âwedge designs, and nonÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Ârandomized studies of interventions (NRSIs), including interrupted time series (ITS) studies, controlled beforeÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âafter (CBA) studies, and followÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âup (cohort) studies containing concurrent controls that focused on or described implementation strategies of WHO guidelines for the prevention, detection, and treatment of PPH. Participants were birth attendants and people giving birth in a hospital or healthcare facility. We excluded studies that did not implement a WHO PPH recommendation, had no comparator group, or did not report clinical/implementation outcomes. Outcomes Our critical outcomes were: adherence to WHOÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Ârecommended guidelines for PPH prevention, detection, and treatment; PPH ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã‚Â°Ãƒâ€šÃ‚Â¥ 500 mL; PPH ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã‚Â°Ãƒâ€šÃ‚Â¥ 1000 mL; additional uterotonics within 24 hours after birth; blood transfusions; maternal death; severe morbidities (major surgery; admission to intensive care unit [ICU]); and adverse effects (variable and related to the clinical intervention) during hospitalization for birth. Our important outcomes were: breastfeeding at discharge; implementation outcomes such as acceptability, adoption, appropriateness, feasibility, fidelity, implementation cost, penetration, and sustainability of the implementation strategy; and health professional outcomes such as knowledge and skill. Risk of bias We used the RoB 2 and ROBINSÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂI tools to assess risk of bias in RCTs and NRSIs, respectively. Synthesis methods Two review authors independently selected studies, performed data extraction, and assessed risk of bias and trustworthiness. Due to the nature of the data, we reported relevant results for each comparison and outcome but did not attempt quantitative synthesis. We used GRADE to assess the certainty of evidence. Included studies We included 13 studies (9 clusterÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂRCTs and 4 NRSIs) with a total of 1,027,273 births and more than 4373 birth attendants. The included studies were conducted in 17 different countries. Most trials were conducted in resourceÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âlimited settings. None of the included studies reported data on the use of additional uterotonics within 24 hours after birth or adverse effects. Synthesis of results SingleÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcomponent implementation strategies versus usual care for PPH prevention, detection, and treatment We do not know if singleÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcomponent implementation strategies have any effect on adherence to WHO PPH prevention recommendations, PPH ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã‚Â°Ãƒâ€šÃ‚Â¥ 500 mL, PPH ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã‚Â°Ãƒâ€šÃ‚Â¥ 1000 mL, or blood transfusion (very lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). LowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence suggests that singleÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcomponent implementation strategies may have little to no effect on maternal death (86,788 births, 3 trials); may increase severe morbidity related to ICU admission (26,985 births, 1 trial); and may reduce severe morbidity related to surgical outcomes (26,985 births, 1 trial). No trials in this comparison measured the effect on adherence to WHO treatment guidelines. Multicomponent implementation strategies versus usual care for PPH prevention, detection, and treatment We do not know if multicomponent implementation strategies have any effect on adherence to WHO PPH treatment recommendations, PPH ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã‚Â°Ãƒâ€šÃ‚Â¥ 500 mL, blood transfusion, or severe morbidity relating to surgical outcomes (very lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). Multicomponent implementation strategies may have little to no effect on matern l death (274,008 births, 2 trials; lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence) compared to usual care. No trials in this comparison measured the effect on adherence to WHO PPH prevention recommendations, PPH ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã‚Â°Ãƒâ€šÃ‚Â¥ 1000 mL, or severe morbidity (outcomes related to ICU admission). Multicomponent implementation strategies versus enhanced usual care for PPH prevention, detection, and treatment LowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence suggests that multicomponent implementation strategies may improve adherence to WHO PPH prevention recommendations (14,718 births, 2 trials) and adherence to WHO PPH treatment recommendations (356,913 births, 2 trials) compared to enhanced usual care. Multicomponent implementation strategies probably have little to no effect on maternal death (224,850 births, 2 trials; moderateÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence), severe morbidity related to ICU admission (224,850 births, 2 trials; moderateÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence), and surgical morbidity (210,132 births, 1 trial; moderateÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence) compared to enhanced usual care. We do not know if multicomponent implementation strategies affect PPH ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã‚Â°Ãƒâ€šÃ‚Â¥ 500 mL, PPH ÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â€šÂ¬Ã‚Â°Ãƒâ€šÃ‚Â¥ 1000 mL, or blood transfusion (very lowÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcertainty evidence). Authors' conclusions Multicomponent implementation strategies may improve adherence to WHO PPH prevention and treatment recommendations, but they probably result in little to no difference in ICU admissions, surgical morbidity, or maternal death. The majority of available evidence is of low to very low certainty, thus we cannot draw any robust conclusions on the effects of implementation strategies for WHO guidelines to prevent, detect, and treat PPH. While all included studies used the implementation strategy of 'train and educate,' the effects seem to be limited when used as a single strategy. Additional research using pragmatic, hybrid effectivenessÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âimplementation study designs that measure implementation outcomes simultaneously alongside clinical outcomes would be beneficial to understand contextual factors, barriers, and facilitators that affect implementation. Funding This Cochrane review had no dedicated external funding. Dr Rose Molina, who is employed by Beth Israel Deaconess Medical Center, received funding from Ariadne Labs (Harvard T.H. Chan School of Public Health, Brigham and Women's Hospital) for her time. As a funder, Ariadne Labs had no involvement in the development of the protocol or conduct of the review. The views and opinions expressed therein are those of the review authors and do not necessarily reflect those of Ariadne Labs. Registration Registration: PROSPERO (CRD42024563802) available via https://www.crd.york.ac.uk/prospero/display_record.php?ID=CRD42024563802 Plain language summary What are the best strategies to implement World Health Organization (WHO) recommendations to prevent, detect, and treat postpartum hemorrhage? Key messages Multicomponent implementation strategies may improve adherence to World Health Organization (WHO) postpartum hemorrhage (PPH) prevention recommendations and probably do not make a difference to intensive care unit (ICU) admissions, need for additional surgeries, or death of the mother. We do not know if multicomponent implementation strategies affect blood loss or blood transfusion. We do not know if singleÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcomponent implementation strategies affect adherence to WHO PPH prevention recommendations, blood loss, or blood transfusion. SingleÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcomponent implementation strategies may not make a difference to the death of the mother, may increase ICU admissions, and may reduce the need for additional surgeries. The small number of studies and differences in data collected across included studies limited our ability to draw any conclusions on effective implementation strategies; however, there were varying degrees of success with identical implementation strategies in different studies, highlighting the need for future research in this area. What is postpartum hemorrhage (PPH)? Postpartum hemorrhage is typically defined as blood loss greater than 500 mL within 24 hours after birth. How is PPH prevented, diagnosed, and reated? WHO guidelines recommend oxytocin administration immediately after birth to prevent PPH. Some birth facilities use blood collection drapes and scales to measure blood loss; however, many do not have access to these supplies. The treatment of PPH varies based on the severity, underlying cause, and available resources. Most cases of PPH are treated with medications that cause the uterus to contract. In women who do not respond to this medication, uterine balloon tamponade (where a balloon is inflated in the uterus to compress blood vessels and stop bleeding) or surgery is needed. What are implementation strategies? Implementation strategies are specific techniques used to increase the acceptance, uptake, and sustainability of a clinical practice or program. Examples include engaging individuals and leaders, changing infrastructure, and training and educating and/or supporting birth attendants. How are implementation strategies used to prevent, diagnose, and treat PPH? A wide range of implementation strategies have been used in clinical practice to prevent, diagnose, and treat PPH. Strategies include training and educating skilled birth attendants in evidenceÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âbased practices, introducing new equipment to birth facilities, and developing reporting systems to audit health records and provide feedback to healthcare workers. What did we want to find out? We wanted to know which, if any, implementation strategies of WHO PPH recommendations are effective in facilityÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âbased childbirth settings. What did we do? We searched for studies that looked at the effects of implementation strategies of WHO PPH recommendations by birth attendants on people who gave birth in a health facility. We summarized the results of the studies and rated our confidence in the evidence based on factors such as study methods and sizes. What did we find out? We included 13 studies, which were categorized into three groups based on the implementation strategies used: (1) single strategy versus usual care, (2) multiple strategies versus usual care, and (3) multiple strategies versus enhanced usual care. We do not know if singleÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcomponent implementation strategies affect adherence to WHO PPH prevention recommendations, blood loss, or blood transfusion. SingleÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âcomponent implementation strategies may not make a difference to maternal death, may reduce the need for additional surgeries, but may also increase ICU admissions. Multicomponent implementation strategies may improve adherence to PPH prevention recommendations and probably do not make a difference to ICU admissions, need for additional surgeries, or maternal death. We do not know if multicomponent implementation strategies affect blood loss or blood transfusion. We found that the same implementation strategies and study approach can increase adherence to WHO guidelines in one setting, not make any difference in another, and even reduce adherence in others. Many studies lacked a comprehensive framework that linked implementation efforts with adherence to WHO recommendations and patient outcomes; it is doubtful that multicomponent intervention could address all factors that contribute to PPHÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Ârelated illness or death. It remains unknown whether multiple strategies work in a realÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âworld setting. What are the limitations of the evidence? The level of detail of implementation strategies varied, preventing the combining of studies. There were also differences in the people included in the studies according to facility level, volume of births, and type of delivery. Different study contexts made it difficult to measure the true impact of implementation strategies on outcomes. How upÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚ÂtoÃƒÆ’Ã‚Â¢ÃƒÂ¢Ã¢â‚¬Å¡Ã‚Â¬Ãƒâ€šÃ‚Âdate is this evidence? The evidence is current to 25 April 2024.</t>
   </si>
   <si>
-    <t>The article focuses on clinical and implementation outcomes without explicit mention of cash-releasing savings.</t>
-  </si>
-  <si>
     <t>J6242</t>
   </si>
   <si>
@@ -1099,9 +1024,6 @@
   </si>
   <si>
     <t>Objectives: In the UK, the National Health Service (NHS) provides free medical care to all legal UK residents, spending approximately 10% of its GDP on health. Given the substantial costs associated with hospital visits and inpatient stays, optimizing patient access to healthcare services and managing patient flow is critical. This study presents a cost-effectiveness analysis of a digital postoperative care pathway, focusing on the introduction of the 'Post Op' app, which connects post-surgery patients with their clinical teams for remote follow-up. This innovation aims to address the final mile" of the Enhanced Recovery After Surgery (ERAS) pathway. Method(s): The 'Post Op' app was piloted at a district general hospital, with patients encouraged to use the app for up to 60 days post-surgery. Data were collected through telephone surveys and anonymized questionnaires. Feedback indicated that over 70% of patients felt the app prevented unnecessary healthcare visits, primarily due to the reassurance provided. This finding aligns with qualitative studies suggesting improved patient satisfaction and fewer complications post op, although the direct financial impact had not been quantified prior to this study.Our cost-effectiveness analysis simulated populations with varying levels of postop anxiety and complications. The analysis considered costs associated with avoidable presentations to the Emergency Department (ED), environmental costs, and costs related to antibiotic tolerance and resistance due to late recognition of surgical site infections (SSIs). Result(s): The results demonstrated significant potential savings for NHS resources, estimating that a digitalized postoperative care pathway could save over 60,000 per 100 patients, even accounting for an increased number of outpatient follow-up visits. Key findings include the reduction of inappropriate medical care-seeking episodes, prevention of postoperative complication deterioration, mitigation of environmental costs linked to excessive hospital resource use and patient transport, and alleviation of costs borne by patients. Specifically, savings from avoided ED visits ranged from 22,225 to 43,435 per 100 patients, with additional savings from early detection of SSIs and prevention of antibiotic resistance estimated at 27,909 per 100 patients. Conclusion(s): The study concludes that the 'Post Op' app provides excellent support for postop patients, significantly reducing the number of unnecessary contacts with GPs, hospitals, and EDs. This results in substantial cost savings for both the NHS and patients. Additionally, the early recognition and treatment of SSIs through the app further enhance cost savings, highlighting the app's role in optimizing the final mile of the ERAS pathway. The digital postoperative follow-up tool not only improves patient outcomes but demonstrates a promising approach to healthcare delivery, aligning with the goals of cost efficiency, improving patient care within the NHS. Copyright ÃƒÆ’Ã¢â‚¬Å¡Ãƒâ€šÃ‚Â© 2024"</t>
-  </si>
-  <si>
-    <t>The article explicitly mentions substantial cost savings for the NHS from avoided ED visits and early detection of SSIs.</t>
   </si>
   <si>
     <t>J6267</t>
@@ -1126,9 +1048,6 @@
 &lt;b&gt;CONCLUSIONS&lt;/b&gt;: XPAND was associated with a lower UVR dose to face in patients with XP and was cost-effective.</t>
   </si>
   <si>
-    <t>The article reports cost-effectiveness but does not explicitly mention cash-releasing savings.</t>
-  </si>
-  <si>
     <t>J6281</t>
   </si>
   <si>
@@ -1138,9 +1057,6 @@
     <t>Background: Health promotion for people with mild frailty has the potential to improve health outcomes, but such services are scarce in practice. We developed a personalised, home-based, behaviour change, health promotion intervention (HomeHealth) and assessed its clinical effectiveness and cost-effectiveness in maintaining independent functioning in activities of daily living in older adults with mild frailty. Method(s): This trial was an individual, multicentre, parallel-group, randomised controlled trial done in England. Participants were mainly recruited from general practices in three different areas of England (the London north Thames region, east and north Hertfordshire, and west Yorkshire). Participants were individuals residing in the community who were registered with a general practice, 65 years and older with mild frailty (scoring 5 on the CFS), with a life expectancy of more than 6 months, and with capacity to consent to participate. We excluded adults residing in nursing or care homes, those with moderate-to-severe frailty or with no frailty, those receiving palliative care, and those already case managed (eg, receiving a similar ongoing intervention from the voluntary sector or community service). Eligible participants were randomly assigned 1:1 to either the HomeHealth intervention or to treatment as usual. HomeHealth is a multidomain health promotion intervention delivered by the voluntary sector at home in six sessions over 6 months. The primary outcome was independent functioning (assessed using the modified Barthel Index [BI]) at 12 months. Outcome assessments were masked and were analysed by intention to treat using linear mixed models. Incremental costs and quality-adjusted life-years (QALYs) were calculated using seemingly unrelated regression and bootstrapping. The trial is registered on the ISRCTN registry (ISRCTN54268283). Finding(s): We recruited 388 participants between Jan 8, 2021 and July 2, 2022 (mean age 81 years, SD 6.5; 249 (64%) of 388 were women and 139 (36%) were men). 195 participants were randomly assigned to HomeHealth and 193 to treatment as usual. Median follow-up was 363 days (IQR 356-370) in the HomeHealth group and 362 days (IQR 355-373) in the treatment-as-usual group. HomeHealth did not improve BI scores at 12 months (mean difference 0.250, 95% CI -0.932 to 1.432). HomeHealth was superior to treatment as usual with a negative point estimate for incremental costs (-796; 95% CI -2016 to 424) and positive point estimate for incremental QALYs (0.009, -0.021 to 0.039). There were 55 serious adverse events in the HomeHealth group and 85 in the treatment-as-usual group; none were intervention related. Interpretation(s): HomeHealth is a safe intervention with a high probability of cost-effectiveness, driven by a reduction in unplanned hospital admissions. HomeHealth should be considered as a health promotion intervention for older people with mild frailty. Funding(s): National Institute for Health Research Health Technology Assessment. Copyright ÃƒÆ’Ã¢â‚¬Å¡Ãƒâ€šÃ‚Â© 2024 The Author(s)</t>
   </si>
   <si>
-    <t>The article reports a negative point estimate for incremental costs indicating a net saving.</t>
-  </si>
-  <si>
     <t>J6282</t>
   </si>
   <si>
@@ -1168,9 +1084,6 @@
     <t>Introduction and Objectives: Non-invasive tests (NITs) identifying high-risk MASLD in primary care is suggested but, these strategies cost-effectiveness remain uncertain in the United Kingdom (UK). Material(s) and Method(s): A cost-utility/budget impact model was developed for cost-effectiveness evaluation of two screening strategies (1) FIB-4 followed by Enhanced Liver Fibrosis (ELF) (FIB-4/ELF); (2) FIB-4 followed by Transient Elastography (FIB-4/TE) compared to standard of care (SoC). A cohort of primary care MASLD patients with an advanced fibrosis prevalence of 4.20 % was simulated. A decision tree classified patients as true positives, false positives, true negatives, or false negatives based on NIT diagnostic accuracy, followed by a 3-year Markov model to estimate costs and quality-adjusted life years (QALYs). The model included 11 health states: MASLD, fibrosis stages (F0-F3), cirrhosis, decompensated cirrhosis, liver transplant, and death. Costs came from the National Tariff, National Schedule of Costs and Personal Social Services Research Unit. Result(s): SoC had a false diagnosis rate of 36.26 %, while FIB-4 with ELF or TE reduced false positive rates to 23.20 % and 20.91 %, respectively. Compared to 112,807 unnecessary hepatology referrals under SoC, FIB-4/ELF or FIB-4/TE reduced unnecessary referrals by 38,031 (33.71 %) and 45,767 (40.57 %), respectively. Both strategies demonstrated cost-effectiveness relative to SoC with total cost per patient of GBP 983.37 for FIB-4/TE, GBP 993.15 for FIB-4/ELF compared to SoC, GBP 1,014.15. Conclusion(s): Sequential NIT screening strategies, combining FIB-4 with ELF or TE, are cost-saving, reduce unnecessary hepatology referrals, and offer an efficient (improve outcomes and reduce healthcare costs) approach for managing high-risk MASLD in UK primary care. Copyright ÃƒÆ’Ã¢â‚¬Å¡Ãƒâ€šÃ‚Â© 2025 Fundacion Clinica Medica Sur, A.C.</t>
   </si>
   <si>
-    <t>The article explicitly states that the strategies are cost-saving and reduce unnecessary referrals.</t>
-  </si>
-  <si>
     <t>J1789</t>
   </si>
   <si>
@@ -1180,9 +1093,6 @@
     <t>Background: Prevention of secondary stroke following initial ictus is an important focus of after-stroke care. Blood pressure (BP) is a key risk factor, so usual care following stroke or transient ischaemic attack includes regular BP checks and monitoring of anti-hypertensive medication. This is traditionally carried out in primary care, but the evidence supporting self-monitoring and self-guided management of BP in the general population with hypertension is growing. Objective(s): Our objective was to estimate the cost effectiveness of treatment as usual (TAU) versus (1) self-monitoring of BP (S-MON) and (2) self-monitoring and guided self-management of anti-hypertensive medication (S-MAN). Method(s): This was a within-trial economic evaluation of a randomised controlled trial estimating the incremental cost per 1 mmHg BP reduction and per quality-adjusted life-year (QALY) gained over a 6-month time horizon from the perspective of the UK National Health Service (NHS). Result(s): Data were evaluable for 140 participants. Costs per patient were 473, 853 and 1035; mean reduction in systolic BP (SBP) was 3.6, 6.7 and 6.1 mmHg, and QALYs accrued were 0.427, 0.422 and 0.423 for TAU, S-MON and S-MAN, respectively. No statistically significant differences in incremental costs or outcomes were detected. On average, S-MAN was dominated or extended dominated. The incremental cost per 1 mmHg BP reduction from S-MON versus TAU was 137. Conclusion(s): On average, S-MAN is an inefficient intervention. S-MON may be cost effective, depending on the willingness to pay for a 1 mmHg BP reduction, although it yielded fewer QALYs over the within-trial time horizon. Decision modelling is required to explore the longer-term costs and outcomes. Copyright ÃƒÆ’Ã¢â‚¬Å¡Ãƒâ€šÃ‚Â© 2020, The Author(s).</t>
   </si>
   <si>
-    <t>The article only reports cost-effectiveness and does not demonstrate explicit cash-releasing savings.</t>
-  </si>
-  <si>
     <t>J1793</t>
   </si>
   <si>
@@ -1208,9 +1118,6 @@
   </si>
   <si>
     <t>Objective: The aim of this study was to determine whether machine learning could reduce the number of mammograms the radiologist must read by using a machine-learning classifier to correctly identify normal mammograms and to select the uncertain and abnormal examinations for radiological interpretation. Method(s): Mammograms in a research data set from over 7,000 women who were recalled for assessment at six UK National Health Service Breast Screening Program centers were used. A convolutional neural network in conjunction with multitask learning was used to extract imaging features from mammograms that mimic the radiological assessment provided by a radiologist, the patient's nonimaging features, and pathology outcomes. A deep neural network was then used to concatenate and fuse multiple mammogram views to predict both a diagnosis and a recommendation of whether or not additional radiological assessment was needed. Result(s): Ten-fold cross-validation was used on 2,000 randomly selected patients from the data set; the remainder of the data set was used for convolutional neural network training. While maintaining an acceptable negative predictive value of 0.99, the proposed model was able to identify 34% (95% confidence interval, 25%-43%) and 91% (95% confidence interval: 88%-94%) of the negative mammograms for test sets with a cancer prevalence of 15% and 1%, respectively. Conclusion(s): Machine learning was leveraged to successfully reduce the number of normal mammograms that radiologists need to read without degrading diagnostic accuracy. Copyright ÃƒÆ’Ã¢â‚¬Å¡Ãƒâ€šÃ‚Â© 2019 American College of Radiology</t>
-  </si>
-  <si>
-    <t>The article focuses on workflow efficiency without explicit cash-releasing savings.</t>
   </si>
   <si>
     <t>J1807</t>
@@ -1276,9 +1183,6 @@
     <t>The article explicitly mentions cost savings through genetic-based dose individualisation.</t>
   </si>
   <si>
-    <t>['cost saving']</t>
-  </si>
-  <si>
     <t>J3624</t>
   </si>
   <si>
@@ -1288,9 +1192,6 @@
     <t>Background: The incidence of cardiac implantable electronic device (CIED) infections is rising. Purpose(s): We examined the factors associated with CIED infection, assessed the prognostic power of the PADIT risk score, and modelled the cost-utility of selective TYRX antimicrobial envelope use for preventing CIED infections. Method(s): Data were extracted from 2016 to 2019, and included all de novo implants, generator changes and lead interventions for transvenous CIEDs at a high-volume UK centre. CIED infection was defined as hospitalisation for device infection within 12 months of a procedure. Cost-utility analysis was informed by standardised tariffs, and quality adjusted life year (QALY) and efficacy data was extrapolated from analysis of the WRAP-IT trial. Result(s): 6,035 patients underwent 7,383 procedures; CIED infection occurred in 59 individuals (0.8%). In addition to the constituents of the PA- DIT score, lead extraction (HR 3.3 (1.9-6.1), p&lt;0.0001), C-reactive protein &gt;50mg/l (HR 3.0 (1.4-6.4), p=0.005), re-intervention within two years (HR 10.1 (5.6-17.9), p&lt;0.0001), and procedure duration over two hours (HR 2.6 (1.6-4.1), p=0.001) were independent predictors of infection. Increased PADIT score was strongly associated with infection (AUC: 0.82, HR per point increase: 1.36 (1.27-1.47), p&lt;0.0001). A cost-utility model assigning TYRX envelopes to patients with PADIT scores &gt;=6 predicted a reduction in infections (number needed to treat: 72) and a cost per QALY gained within the UK's (NICE) cost-effectiveness threshold (25,107). Conclusion(s): The PADIT score was a powerful predictor of CIED infections in a heterogeneous population,and may facilitate cost-effective TYRX envelope allocation in selected high-risk patients. (Figure presented).</t>
   </si>
   <si>
-    <t>The article only reports cost-effectiveness and QALY without explicit cash-releasing savings.</t>
-  </si>
-  <si>
     <t>J3630</t>
   </si>
   <si>
@@ -1309,9 +1210,6 @@
     <t>Purpose: In Sheffield (UK), we introduced the PINP monitoring algorithm for the management of osteoporosis treatment delivered in primary care. Our aims were to evaluate whether this algorithm was associated with better osteoporosis outcomes and was cost-effective compared to standard care. Method(s): Inclusion criteria were referral from Sheffield GPs, BMD scans performed between 2012 and 2013 and a report advising initiation of oral bisphosphonate and PINP monitoring. 906 patients were identified and retrospectively divided into Group A (intention to monitor, with baseline PINP, n = 588) and Group B (no intention to monitor, without baseline PINP, n = 318). The model described by Davis and colleagues was used to extrapolate life-time costs and quality-adjusted life-years (QALYs). Result(s): No differences were found in baseline characteristics between groups (age, gender, BMI, BMD and major risk factors for fractures). More patients in Group A started oral treatment (77.4% vs 49.1%; p &lt; 0.001), but there were no differences between groups in the presence of a gap in treatment &gt;3 months or in treatment duration. Patients in Group A were more likely to have follow-up DXA scan at 4-6 years from baseline (46.9% vs 29.2%; p &lt; 0.000) and had a greater increase in total hip BMD (+2.74% vs + 0.42%; p value = 0.003). Fewer new fractures occurred in Group A but this was not statistically significant, but the numbers of fractures were small. Patients in Group A were more likely to change management (p = 0.005) including switching to zoledronate (p = 0.03). The PINP measurement and increased prescribing in Group A resulted in increases in both costs (30.19) and QALYs (0.0039) relative to Group B, giving an incremental cost effectiveness ratio (ICER) of 7660 in the probabilistic sensitivity analysis. Conclusion(s): Patients monitored with PINP are more likely to start oral bisphosphonate treatment, switch to zoledronate, have follow-up DXA scans and a greater increase of hip BMD. PINP monitoring has the potential to be cost-effective in a UK NHS setting given that interventions with an ICER under 20,000 are generally considered to be cost-effective. Copyright ÃƒÆ’Ã¢â‚¬Å¡Ãƒâ€šÃ‚Â© 2022 The Authors</t>
   </si>
   <si>
-    <t>The article only reports cost-effectiveness (ICER) without explicit cash-releasing savings.</t>
-  </si>
-  <si>
     <t>Reason</t>
   </si>
   <si>
@@ -1409,6 +1307,93 @@
   </si>
   <si>
     <t>include_stage_6</t>
+  </si>
+  <si>
+    <t>The article focuses on clinical outcomes without explicit mention of cash-releasing savings or ROI.</t>
+  </si>
+  <si>
+    <t>The article discusses economic burden but does not explicitly demonstrate cash-releasing savings or positive ROI.</t>
+  </si>
+  <si>
+    <t>The article focuses on clinical outcomes without explicit mention of cash-releasing savings or positive ROI.</t>
+  </si>
+  <si>
+    <t>The article focuses on clinical outcomes without explicit mention of cash-releasing savings or net budget impact.</t>
+  </si>
+  <si>
+    <t>The article only reports cost-effectiveness (ICER, QALY) without explicit savings.</t>
+  </si>
+  <si>
+    <t>The article focuses on cost-effectiveness without explicit savings.</t>
+  </si>
+  <si>
+    <t>The article reports ROI without explicit cash-releasing savings.</t>
+  </si>
+  <si>
+    <t>The article reports an incremental cost saving per person, indicating a net saving.</t>
+  </si>
+  <si>
+    <t>The article only reports cost-effectiveness without explicit savings.</t>
+  </si>
+  <si>
+    <t>The study does not demonstrate explicit cash-releasing savings or positive ROI.</t>
+  </si>
+  <si>
+    <t>The article estimates potential cumulative direct cost savings over 5 years.</t>
+  </si>
+  <si>
+    <t>No explicit cash-releasing savings or net benefit stated</t>
+  </si>
+  <si>
+    <t>The article focuses on clinical outcomes and treatment efficacy without explicit mention of cash-releasing savings or net budget impact.</t>
+  </si>
+  <si>
+    <t>The article discusses cost-effectiveness but does not explicitly state cash-releasing savings or positive ROI.</t>
+  </si>
+  <si>
+    <t>No explicit cash-releasing savings or positive ROI reported.</t>
+  </si>
+  <si>
+    <t>The article explicitly states a cost saving of 6270 over a short period.</t>
+  </si>
+  <si>
+    <t>The article focuses on clinical outcomes and does not explicitly demonstrate cash-releasing savings or positive ROI.</t>
+  </si>
+  <si>
+    <t>The article reports cost reductions explicitly.</t>
+  </si>
+  <si>
+    <t>The article reports a reduction in readmission costs, indicating expenditure reduction.</t>
+  </si>
+  <si>
+    <t>The article reports healthcare cost savings of 746 per participant.</t>
+  </si>
+  <si>
+    <t>The article only discusses potential cost-effectiveness without explicit savings.</t>
+  </si>
+  <si>
+    <t>The article focuses on clinical outcomes and implementation strategies without explicit mention of cash-releasing savings or positive ROI.</t>
+  </si>
+  <si>
+    <t>The article mentions cost-savings but does not explicitly state cash-releasing savings or net savings.</t>
+  </si>
+  <si>
+    <t>The article explicitly mentions substantial cost savings for the NHS.</t>
+  </si>
+  <si>
+    <t>The article reports a negative point estimate for incremental costs, indicating a negative net budget impact.</t>
+  </si>
+  <si>
+    <t>['negative net budget impact']</t>
+  </si>
+  <si>
+    <t>The article states that the strategies are cost-saving and reduce unnecessary referrals.</t>
+  </si>
+  <si>
+    <t>The article focuses on workflow efficiency without explicit mention of cash-releasing savings.</t>
+  </si>
+  <si>
+    <t>The article only reports cost-effectiveness (ICER) without explicit savings.</t>
   </si>
 </sst>
 </file>
@@ -1501,7 +1486,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="10">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1599,36 +1584,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2008,10 +1963,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>138</v>
+        <v>288</v>
       </c>
       <c r="G2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H2">
         <v>0.95</v>
@@ -2034,10 +1989,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H3">
         <v>0.9</v>
@@ -2054,19 +2009,19 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
         <v>141</v>
       </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
-        <v>142</v>
-      </c>
       <c r="G4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H4">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -2080,16 +2035,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>144</v>
+        <v>289</v>
       </c>
       <c r="G5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H5">
         <v>0.9</v>
@@ -2106,16 +2061,16 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G6" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="H6">
         <v>0.9</v>
@@ -2129,19 +2084,19 @@
         <v>2019</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H7">
         <v>0.9</v>
@@ -2155,19 +2110,19 @@
         <v>2019</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>152</v>
+        <v>290</v>
       </c>
       <c r="G8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H8">
         <v>0.9</v>
@@ -2190,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>153</v>
+        <v>291</v>
       </c>
       <c r="G9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H9">
         <v>0.9</v>
@@ -2210,16 +2165,16 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>155</v>
+        <v>292</v>
       </c>
       <c r="G10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -2242,13 +2197,13 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>156</v>
+        <v>293</v>
       </c>
       <c r="G11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H11">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -2268,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>157</v>
+        <v>294</v>
       </c>
       <c r="G12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H12">
         <v>0.9</v>
@@ -2291,13 +2246,13 @@
         <v>28</v>
       </c>
       <c r="E13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>158</v>
+        <v>295</v>
       </c>
       <c r="G13" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="H13">
         <v>0.9</v>
@@ -2320,10 +2275,10 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="G14" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H14">
         <v>0.9</v>
@@ -2346,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>161</v>
+        <v>296</v>
       </c>
       <c r="G15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H15">
         <v>0.9</v>
@@ -2372,10 +2327,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H16">
         <v>0.9</v>
@@ -2392,16 +2347,16 @@
         <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="G17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H17">
         <v>0.9</v>
@@ -2424,10 +2379,10 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="G18" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H18">
         <v>0.9</v>
@@ -2444,16 +2399,16 @@
         <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>152</v>
+        <v>291</v>
       </c>
       <c r="G19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H19">
         <v>0.9</v>
@@ -2470,16 +2425,16 @@
         <v>98</v>
       </c>
       <c r="D20" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="G20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H20">
         <v>0.9</v>
@@ -2502,10 +2457,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>167</v>
+        <v>297</v>
       </c>
       <c r="G21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H21">
         <v>0.9</v>
@@ -2528,10 +2483,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>168</v>
+        <v>296</v>
       </c>
       <c r="G22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H22">
         <v>0.9</v>
@@ -2554,10 +2509,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>169</v>
+        <v>296</v>
       </c>
       <c r="G23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H23">
         <v>0.9</v>
@@ -2580,10 +2535,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>170</v>
+        <v>290</v>
       </c>
       <c r="G24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H24">
         <v>0.9</v>
@@ -2600,16 +2555,16 @@
         <v>100</v>
       </c>
       <c r="D25" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>172</v>
+        <v>298</v>
       </c>
       <c r="G25" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H25">
         <v>0.9</v>
@@ -2632,10 +2587,10 @@
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H26">
         <v>0.9</v>
@@ -2658,13 +2613,13 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H27">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
@@ -2678,16 +2633,16 @@
         <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>174</v>
+        <v>299</v>
       </c>
       <c r="G28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H28">
         <v>0.9</v>
@@ -2710,10 +2665,10 @@
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="G29" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="H29">
         <v>0.9</v>
@@ -2727,19 +2682,19 @@
         <v>2021</v>
       </c>
       <c r="C30" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="D30" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>179</v>
+        <v>300</v>
       </c>
       <c r="G30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H30">
         <v>0.9</v>
@@ -2753,19 +2708,19 @@
         <v>2021</v>
       </c>
       <c r="C31" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="D31" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H31">
         <v>0.9</v>
@@ -2788,13 +2743,13 @@
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="G32" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H32">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
@@ -2814,10 +2769,10 @@
         <v>0</v>
       </c>
       <c r="F33" t="s">
-        <v>183</v>
+        <v>301</v>
       </c>
       <c r="G33" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H33">
         <v>0.9</v>
@@ -2840,10 +2795,10 @@
         <v>0</v>
       </c>
       <c r="F34" t="s">
-        <v>184</v>
+        <v>302</v>
       </c>
       <c r="G34" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -2866,10 +2821,10 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>185</v>
+        <v>303</v>
       </c>
       <c r="G35" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="H35">
         <v>0.9</v>
@@ -2883,19 +2838,19 @@
         <v>2021</v>
       </c>
       <c r="C36" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="D36" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="G36" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H36">
         <v>0.9</v>
@@ -2918,10 +2873,10 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="G37" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H37">
         <v>0.9</v>
@@ -2944,13 +2899,13 @@
         <v>0</v>
       </c>
       <c r="F38" t="s">
-        <v>182</v>
+        <v>304</v>
       </c>
       <c r="G38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H38">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
@@ -2970,10 +2925,10 @@
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>190</v>
+        <v>305</v>
       </c>
       <c r="G39" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H39">
         <v>0.9</v>
@@ -2990,19 +2945,19 @@
         <v>125</v>
       </c>
       <c r="D40" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>161</v>
+        <v>292</v>
       </c>
       <c r="G40" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H40">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
@@ -3022,13 +2977,13 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H41">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
@@ -3048,10 +3003,10 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>192</v>
+        <v>306</v>
       </c>
       <c r="G42" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H42">
         <v>0.9</v>
@@ -3068,16 +3023,16 @@
         <v>133</v>
       </c>
       <c r="D43" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H43">
         <v>0.95</v>
@@ -3097,13 +3052,13 @@
         <v>83</v>
       </c>
       <c r="E44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>194</v>
+        <v>307</v>
       </c>
       <c r="G44" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="H44">
         <v>0.9</v>
@@ -3126,10 +3081,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H45">
         <v>0.9</v>
@@ -3146,16 +3101,16 @@
         <v>135</v>
       </c>
       <c r="D46" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="G46" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H46">
         <v>0.9</v>
@@ -3163,25 +3118,25 @@
     </row>
     <row r="47" spans="1:8" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="B47">
         <v>2025</v>
       </c>
       <c r="C47" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>199</v>
+        <v>308</v>
       </c>
       <c r="G47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H47">
         <v>0.9</v>
@@ -3189,25 +3144,25 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="B48">
         <v>2025</v>
       </c>
       <c r="C48" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="D48" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>203</v>
+        <v>139</v>
       </c>
       <c r="G48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H48">
         <v>0.9</v>
@@ -3215,25 +3170,25 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="B49">
         <v>2025</v>
       </c>
       <c r="C49" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="D49" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>207</v>
+        <v>309</v>
       </c>
       <c r="G49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H49">
         <v>0.9</v>
@@ -3241,51 +3196,51 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="B50">
         <v>2025</v>
       </c>
       <c r="C50" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="D50" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>203</v>
+        <v>310</v>
       </c>
       <c r="G50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H50">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="B51">
         <v>2025</v>
       </c>
       <c r="C51" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="D51" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G51" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H51">
         <v>0.9</v>
@@ -3293,25 +3248,25 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="B52">
         <v>2025</v>
       </c>
       <c r="C52" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="D52" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G52" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H52">
         <v>0.9</v>
@@ -3319,25 +3274,25 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="B53">
         <v>2025</v>
       </c>
       <c r="C53" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="D53" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="E53" t="b">
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="G53" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H53">
         <v>0.8</v>
@@ -3345,25 +3300,25 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="B54">
         <v>2025</v>
       </c>
       <c r="C54" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="D54" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="E54" t="b">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>224</v>
+        <v>311</v>
       </c>
       <c r="G54" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H54">
         <v>0.9</v>
@@ -3371,25 +3326,25 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="B55">
         <v>2025</v>
       </c>
       <c r="C55" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="D55" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G55" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H55">
         <v>0.9</v>
@@ -3397,25 +3352,25 @@
     </row>
     <row r="56" spans="1:8" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="B56">
         <v>2025</v>
       </c>
       <c r="C56" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="G56" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H56">
         <v>0.9</v>
@@ -3423,25 +3378,25 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="B57">
         <v>2025</v>
       </c>
       <c r="C57" t="s">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="D57" t="s">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="E57" t="b">
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>235</v>
+        <v>312</v>
       </c>
       <c r="G57" t="s">
-        <v>186</v>
+        <v>313</v>
       </c>
       <c r="H57">
         <v>0.9</v>
@@ -3449,51 +3404,51 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="B58">
         <v>2025</v>
       </c>
       <c r="C58" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="D58" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="s">
-        <v>161</v>
+        <v>292</v>
       </c>
       <c r="G58" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H58">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="B59">
         <v>2025</v>
       </c>
       <c r="C59" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="D59" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>169</v>
+        <v>296</v>
       </c>
       <c r="G59" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H59">
         <v>0.9</v>
@@ -3501,25 +3456,25 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="B60">
         <v>2025</v>
       </c>
       <c r="C60" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="D60" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="E60" t="b">
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>245</v>
+        <v>314</v>
       </c>
       <c r="G60" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H60">
         <v>0.9</v>
@@ -3527,51 +3482,51 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>246</v>
+        <v>217</v>
       </c>
       <c r="B61">
         <v>2020</v>
       </c>
       <c r="C61" t="s">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="D61" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="s">
-        <v>249</v>
+        <v>296</v>
       </c>
       <c r="G61" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H61">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="B62">
         <v>2020</v>
       </c>
       <c r="C62" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="D62" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="G62" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H62">
         <v>0.9</v>
@@ -3579,25 +3534,25 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="B63">
         <v>2020</v>
       </c>
       <c r="C63" t="s">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="D63" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G63" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H63">
         <v>0.9</v>
@@ -3605,25 +3560,25 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="B64">
         <v>2020</v>
       </c>
       <c r="C64" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
       <c r="D64" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="s">
-        <v>259</v>
+        <v>315</v>
       </c>
       <c r="G64" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H64">
         <v>0.9</v>
@@ -3631,25 +3586,25 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>260</v>
+        <v>229</v>
       </c>
       <c r="B65">
         <v>2020</v>
       </c>
       <c r="C65" t="s">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="D65" t="s">
-        <v>262</v>
+        <v>231</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G65" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H65">
         <v>0.9</v>
@@ -3657,25 +3612,25 @@
     </row>
     <row r="66" spans="1:8" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="B66">
         <v>2022</v>
       </c>
       <c r="C66" t="s">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G66" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H66">
         <v>0.9</v>
@@ -3683,25 +3638,25 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>266</v>
+        <v>235</v>
       </c>
       <c r="B67">
         <v>2022</v>
       </c>
       <c r="C67" t="s">
-        <v>267</v>
+        <v>236</v>
       </c>
       <c r="D67" t="s">
-        <v>268</v>
+        <v>237</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="s">
-        <v>269</v>
+        <v>238</v>
       </c>
       <c r="G67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H67">
         <v>0.9</v>
@@ -3709,25 +3664,25 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
       <c r="B68">
         <v>2022</v>
       </c>
       <c r="C68" t="s">
-        <v>271</v>
+        <v>240</v>
       </c>
       <c r="D68" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="s">
-        <v>138</v>
+        <v>291</v>
       </c>
       <c r="G68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H68">
         <v>0.95</v>
@@ -3735,25 +3690,25 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>273</v>
+        <v>242</v>
       </c>
       <c r="B69">
         <v>2022</v>
       </c>
       <c r="C69" t="s">
-        <v>274</v>
+        <v>243</v>
       </c>
       <c r="D69" t="s">
-        <v>275</v>
+        <v>244</v>
       </c>
       <c r="E69" t="b">
         <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>276</v>
+        <v>245</v>
       </c>
       <c r="G69" t="s">
-        <v>277</v>
+        <v>167</v>
       </c>
       <c r="H69">
         <v>0.9</v>
@@ -3761,25 +3716,25 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="B70">
         <v>2022</v>
       </c>
       <c r="C70" t="s">
-        <v>279</v>
+        <v>247</v>
       </c>
       <c r="D70" t="s">
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="G70" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H70">
         <v>0.9</v>
@@ -3787,25 +3742,25 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>282</v>
+        <v>249</v>
       </c>
       <c r="B71">
         <v>2022</v>
       </c>
       <c r="C71" t="s">
-        <v>283</v>
+        <v>250</v>
       </c>
       <c r="D71" t="s">
-        <v>284</v>
+        <v>251</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>169</v>
+        <v>296</v>
       </c>
       <c r="G71" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H71">
         <v>0.9</v>
@@ -3813,28 +3768,28 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>285</v>
+        <v>252</v>
       </c>
       <c r="B72">
         <v>2022</v>
       </c>
       <c r="C72" t="s">
-        <v>286</v>
+        <v>253</v>
       </c>
       <c r="D72" t="s">
-        <v>287</v>
+        <v>254</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72" t="s">
-        <v>288</v>
+        <v>316</v>
       </c>
       <c r="G72" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H72">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -4079,132 +4034,132 @@
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>246</v>
+        <v>217</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>260</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>263</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>266</v>
+        <v>235</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>273</v>
+        <v>242</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>282</v>
+        <v>249</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>285</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -4231,13 +4186,13 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>320</v>
+        <v>286</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>289</v>
+        <v>255</v>
       </c>
       <c r="G1" t="s">
-        <v>321</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -4254,10 +4209,10 @@
         <v>137</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G2" t="b">
         <f>IF(E2="EXCLUDE",FALSE,TRUE)</f>
@@ -4278,10 +4233,10 @@
         <v>51</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>292</v>
+        <v>258</v>
       </c>
       <c r="G3" t="b">
         <f t="shared" ref="G3:G66" si="0">IF(E3="EXCLUDE",FALSE,TRUE)</f>
@@ -4299,13 +4254,13 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G4" t="b">
         <f t="shared" si="0"/>
@@ -4323,13 +4278,13 @@
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G5" t="b">
         <f t="shared" si="0"/>
@@ -4347,13 +4302,13 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>294</v>
+        <v>260</v>
       </c>
       <c r="G6" t="b">
         <f t="shared" si="0"/>
@@ -4368,16 +4323,16 @@
         <v>2019</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G7" t="b">
         <f t="shared" si="0"/>
@@ -4392,16 +4347,16 @@
         <v>2019</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G8" t="b">
         <f t="shared" si="0"/>
@@ -4422,10 +4377,10 @@
         <v>52</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G9" t="b">
         <f t="shared" si="0"/>
@@ -4443,13 +4398,13 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G10" t="b">
         <f t="shared" si="0"/>
@@ -4470,10 +4425,10 @@
         <v>22</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G11" t="b">
         <f t="shared" si="0"/>
@@ -4494,10 +4449,10 @@
         <v>25</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>295</v>
+        <v>261</v>
       </c>
       <c r="G12" t="b">
         <f t="shared" si="0"/>
@@ -4518,10 +4473,10 @@
         <v>28</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>296</v>
+        <v>262</v>
       </c>
       <c r="G13" t="b">
         <f t="shared" si="0"/>
@@ -4542,10 +4497,10 @@
         <v>31</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>297</v>
+        <v>263</v>
       </c>
       <c r="G14" t="b">
         <f t="shared" si="0"/>
@@ -4566,10 +4521,10 @@
         <v>89</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>298</v>
+        <v>264</v>
       </c>
       <c r="G15" t="b">
         <f t="shared" si="0"/>
@@ -4590,10 +4545,10 @@
         <v>56</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G16" t="b">
         <f t="shared" si="0"/>
@@ -4611,13 +4566,13 @@
         <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>299</v>
+        <v>265</v>
       </c>
       <c r="G17" t="b">
         <f t="shared" si="0"/>
@@ -4638,10 +4593,10 @@
         <v>94</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="G18" t="b">
         <f t="shared" si="0"/>
@@ -4659,13 +4614,13 @@
         <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G19" t="b">
         <f t="shared" si="0"/>
@@ -4683,13 +4638,13 @@
         <v>98</v>
       </c>
       <c r="D20" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G20" t="b">
         <f t="shared" si="0"/>
@@ -4710,10 +4665,10 @@
         <v>59</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G21" t="b">
         <f t="shared" si="0"/>
@@ -4734,10 +4689,10 @@
         <v>62</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G22" t="b">
         <f t="shared" si="0"/>
@@ -4758,10 +4713,10 @@
         <v>65</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G23" t="b">
         <f t="shared" si="0"/>
@@ -4782,10 +4737,10 @@
         <v>68</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G24" t="b">
         <f t="shared" si="0"/>
@@ -4803,13 +4758,13 @@
         <v>100</v>
       </c>
       <c r="D25" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="G25" t="b">
         <f t="shared" si="0"/>
@@ -4830,10 +4785,10 @@
         <v>71</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G26" t="b">
         <f t="shared" si="0"/>
@@ -4854,10 +4809,10 @@
         <v>103</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G27" t="b">
         <f t="shared" si="0"/>
@@ -4875,13 +4830,13 @@
         <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G28" t="b">
         <f t="shared" si="0"/>
@@ -4902,10 +4857,10 @@
         <v>108</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c r="G29" t="b">
         <f t="shared" si="0"/>
@@ -4920,16 +4875,16 @@
         <v>2021</v>
       </c>
       <c r="C30" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="D30" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G30" t="b">
         <f t="shared" si="0"/>
@@ -4944,16 +4899,16 @@
         <v>2021</v>
       </c>
       <c r="C31" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="D31" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G31" t="b">
         <f t="shared" si="0"/>
@@ -4974,10 +4929,10 @@
         <v>74</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>303</v>
+        <v>269</v>
       </c>
       <c r="G32" t="b">
         <f t="shared" si="0"/>
@@ -4998,10 +4953,10 @@
         <v>77</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G33" t="b">
         <f t="shared" si="0"/>
@@ -5022,10 +4977,10 @@
         <v>113</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G34" t="b">
         <f t="shared" si="0"/>
@@ -5046,10 +5001,10 @@
         <v>116</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="G35" t="b">
         <f t="shared" si="0"/>
@@ -5064,16 +5019,16 @@
         <v>2021</v>
       </c>
       <c r="C36" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="D36" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G36" t="b">
         <f t="shared" si="0"/>
@@ -5094,10 +5049,10 @@
         <v>120</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>305</v>
+        <v>271</v>
       </c>
       <c r="G37" t="b">
         <f t="shared" si="0"/>
@@ -5118,10 +5073,10 @@
         <v>80</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G38" t="b">
         <f t="shared" si="0"/>
@@ -5142,10 +5097,10 @@
         <v>123</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="G39" t="b">
         <f t="shared" si="0"/>
@@ -5163,13 +5118,13 @@
         <v>125</v>
       </c>
       <c r="D40" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G40" t="b">
         <f t="shared" si="0"/>
@@ -5190,10 +5145,10 @@
         <v>128</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G41" t="b">
         <f t="shared" si="0"/>
@@ -5214,10 +5169,10 @@
         <v>131</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>307</v>
+        <v>273</v>
       </c>
       <c r="G42" t="b">
         <f t="shared" si="0"/>
@@ -5235,13 +5190,13 @@
         <v>133</v>
       </c>
       <c r="D43" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G43" t="b">
         <f t="shared" si="0"/>
@@ -5262,10 +5217,10 @@
         <v>83</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>308</v>
+        <v>274</v>
       </c>
       <c r="G44" t="b">
         <f t="shared" si="0"/>
@@ -5286,10 +5241,10 @@
         <v>86</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G45" t="b">
         <f t="shared" si="0"/>
@@ -5307,13 +5262,13 @@
         <v>135</v>
       </c>
       <c r="D46" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G46" t="b">
         <f t="shared" si="0"/>
@@ -5322,22 +5277,22 @@
     </row>
     <row r="47" spans="1:7" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="B47">
         <v>2025</v>
       </c>
       <c r="C47" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G47" t="b">
         <f t="shared" si="0"/>
@@ -5346,22 +5301,22 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="B48">
         <v>2025</v>
       </c>
       <c r="C48" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="D48" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>309</v>
+        <v>275</v>
       </c>
       <c r="G48" t="b">
         <f t="shared" si="0"/>
@@ -5370,22 +5325,22 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="B49">
         <v>2025</v>
       </c>
       <c r="C49" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="D49" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G49" t="b">
         <f t="shared" si="0"/>
@@ -5394,22 +5349,22 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="B50">
         <v>2025</v>
       </c>
       <c r="C50" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="D50" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>310</v>
+        <v>276</v>
       </c>
       <c r="G50" t="b">
         <f t="shared" si="0"/>
@@ -5418,22 +5373,22 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="B51">
         <v>2025</v>
       </c>
       <c r="C51" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="D51" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G51" t="b">
         <f t="shared" si="0"/>
@@ -5442,22 +5397,22 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="B52">
         <v>2025</v>
       </c>
       <c r="C52" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="D52" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G52" t="b">
         <f t="shared" si="0"/>
@@ -5466,22 +5421,22 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="B53">
         <v>2025</v>
       </c>
       <c r="C53" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="D53" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G53" t="b">
         <f t="shared" si="0"/>
@@ -5490,22 +5445,22 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="B54">
         <v>2025</v>
       </c>
       <c r="C54" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="D54" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>311</v>
+        <v>277</v>
       </c>
       <c r="G54" t="b">
         <f t="shared" si="0"/>
@@ -5514,22 +5469,22 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="B55">
         <v>2025</v>
       </c>
       <c r="C55" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="D55" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G55" t="b">
         <f t="shared" si="0"/>
@@ -5538,22 +5493,22 @@
     </row>
     <row r="56" spans="1:7" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="B56">
         <v>2025</v>
       </c>
       <c r="C56" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>312</v>
+        <v>278</v>
       </c>
       <c r="G56" t="b">
         <f t="shared" si="0"/>
@@ -5562,22 +5517,22 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="B57">
         <v>2025</v>
       </c>
       <c r="C57" t="s">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="D57" t="s">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>313</v>
+        <v>279</v>
       </c>
       <c r="G57" t="b">
         <f t="shared" si="0"/>
@@ -5586,22 +5541,22 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="B58">
         <v>2025</v>
       </c>
       <c r="C58" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="D58" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G58" t="b">
         <f t="shared" si="0"/>
@@ -5610,22 +5565,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="B59">
         <v>2025</v>
       </c>
       <c r="C59" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="D59" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G59" t="b">
         <f t="shared" si="0"/>
@@ -5634,22 +5589,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="B60">
         <v>2025</v>
       </c>
       <c r="C60" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="D60" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>314</v>
+        <v>280</v>
       </c>
       <c r="G60" t="b">
         <f t="shared" si="0"/>
@@ -5658,22 +5613,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>246</v>
+        <v>217</v>
       </c>
       <c r="B61">
         <v>2020</v>
       </c>
       <c r="C61" t="s">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="D61" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G61" t="b">
         <f t="shared" si="0"/>
@@ -5682,22 +5637,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="B62">
         <v>2020</v>
       </c>
       <c r="C62" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="D62" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G62" t="b">
         <f t="shared" si="0"/>
@@ -5706,22 +5661,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="B63">
         <v>2020</v>
       </c>
       <c r="C63" t="s">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="D63" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G63" t="b">
         <f t="shared" si="0"/>
@@ -5730,22 +5685,22 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="B64">
         <v>2020</v>
       </c>
       <c r="C64" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
       <c r="D64" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>315</v>
+        <v>281</v>
       </c>
       <c r="G64" t="b">
         <f t="shared" si="0"/>
@@ -5754,22 +5709,22 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>260</v>
+        <v>229</v>
       </c>
       <c r="B65">
         <v>2020</v>
       </c>
       <c r="C65" t="s">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="D65" t="s">
-        <v>262</v>
+        <v>231</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G65" t="b">
         <f t="shared" si="0"/>
@@ -5778,22 +5733,22 @@
     </row>
     <row r="66" spans="1:7" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="B66">
         <v>2022</v>
       </c>
       <c r="C66" t="s">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G66" t="b">
         <f t="shared" si="0"/>
@@ -5802,22 +5757,22 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>266</v>
+        <v>235</v>
       </c>
       <c r="B67">
         <v>2022</v>
       </c>
       <c r="C67" t="s">
-        <v>267</v>
+        <v>236</v>
       </c>
       <c r="D67" t="s">
-        <v>268</v>
+        <v>237</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>316</v>
+        <v>282</v>
       </c>
       <c r="G67" t="b">
         <f t="shared" ref="G67:G72" si="1">IF(E67="EXCLUDE",FALSE,TRUE)</f>
@@ -5826,22 +5781,22 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
       <c r="B68">
         <v>2022</v>
       </c>
       <c r="C68" t="s">
-        <v>271</v>
+        <v>240</v>
       </c>
       <c r="D68" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G68" t="b">
         <f t="shared" si="1"/>
@@ -5850,22 +5805,22 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>273</v>
+        <v>242</v>
       </c>
       <c r="B69">
         <v>2022</v>
       </c>
       <c r="C69" t="s">
-        <v>274</v>
+        <v>243</v>
       </c>
       <c r="D69" t="s">
-        <v>275</v>
+        <v>244</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>317</v>
+        <v>283</v>
       </c>
       <c r="G69" t="b">
         <f t="shared" si="1"/>
@@ -5874,22 +5829,22 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="B70">
         <v>2022</v>
       </c>
       <c r="C70" t="s">
-        <v>279</v>
+        <v>247</v>
       </c>
       <c r="D70" t="s">
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G70" t="b">
         <f t="shared" si="1"/>
@@ -5898,22 +5853,22 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>282</v>
+        <v>249</v>
       </c>
       <c r="B71">
         <v>2022</v>
       </c>
       <c r="C71" t="s">
-        <v>283</v>
+        <v>250</v>
       </c>
       <c r="D71" t="s">
-        <v>284</v>
+        <v>251</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G71" t="b">
         <f t="shared" si="1"/>
@@ -5922,22 +5877,22 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>285</v>
+        <v>252</v>
       </c>
       <c r="B72">
         <v>2022</v>
       </c>
       <c r="C72" t="s">
-        <v>286</v>
+        <v>253</v>
       </c>
       <c r="D72" t="s">
-        <v>287</v>
+        <v>254</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="G72" t="b">
         <f t="shared" si="1"/>
@@ -5981,13 +5936,13 @@
         <v>50</v>
       </c>
       <c r="I1" t="s">
-        <v>320</v>
+        <v>286</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>289</v>
+        <v>255</v>
       </c>
       <c r="K1" t="s">
-        <v>321</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
@@ -6007,19 +5962,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>138</v>
+        <v>288</v>
       </c>
       <c r="G2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H2">
         <v>0.95</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K2" t="b">
         <f>IF(I2="EXCLUDE",FALSE,TRUE)</f>
@@ -6043,19 +5998,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H3">
         <v>0.9</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>292</v>
+        <v>258</v>
       </c>
       <c r="K3" t="b">
         <f t="shared" ref="K3:K66" si="0">IF(I3="EXCLUDE",FALSE,TRUE)</f>
@@ -6073,25 +6028,25 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
         <v>141</v>
       </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
-        <v>142</v>
-      </c>
       <c r="G4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H4">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K4" t="b">
         <f t="shared" si="0"/>
@@ -6109,25 +6064,25 @@
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>144</v>
+        <v>289</v>
       </c>
       <c r="G5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H5">
         <v>0.9</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K5" t="b">
         <f t="shared" si="0"/>
@@ -6145,25 +6100,25 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G6" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="H6">
         <v>0.9</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>294</v>
+        <v>260</v>
       </c>
       <c r="K6" t="b">
         <f t="shared" si="0"/>
@@ -6178,28 +6133,28 @@
         <v>2019</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H7">
         <v>0.9</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K7" t="b">
         <f t="shared" si="0"/>
@@ -6214,28 +6169,28 @@
         <v>2019</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>152</v>
+        <v>290</v>
       </c>
       <c r="G8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H8">
         <v>0.9</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K8" t="b">
         <f t="shared" si="0"/>
@@ -6259,19 +6214,19 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>153</v>
+        <v>291</v>
       </c>
       <c r="G9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H9">
         <v>0.9</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K9" t="b">
         <f t="shared" si="0"/>
@@ -6289,25 +6244,25 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>155</v>
+        <v>292</v>
       </c>
       <c r="G10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K10" t="b">
         <f t="shared" si="0"/>
@@ -6331,19 +6286,19 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>156</v>
+        <v>293</v>
       </c>
       <c r="G11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H11">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K11" t="b">
         <f t="shared" si="0"/>
@@ -6367,26 +6322,26 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>157</v>
+        <v>294</v>
       </c>
       <c r="G12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H12">
         <v>0.9</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>295</v>
+        <v>261</v>
       </c>
       <c r="K12" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -6400,22 +6355,22 @@
         <v>28</v>
       </c>
       <c r="E13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>158</v>
+        <v>295</v>
       </c>
       <c r="G13" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="H13">
         <v>0.9</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>296</v>
+        <v>262</v>
       </c>
       <c r="K13" t="b">
         <f t="shared" si="0"/>
@@ -6439,19 +6394,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="G14" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H14">
         <v>0.9</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>297</v>
+        <v>263</v>
       </c>
       <c r="K14" t="b">
         <f t="shared" si="0"/>
@@ -6475,19 +6430,19 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>161</v>
+        <v>296</v>
       </c>
       <c r="G15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H15">
         <v>0.9</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>298</v>
+        <v>264</v>
       </c>
       <c r="K15" t="b">
         <f t="shared" si="0"/>
@@ -6511,19 +6466,19 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H16">
         <v>0.9</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K16" t="b">
         <f t="shared" si="0"/>
@@ -6541,25 +6496,25 @@
         <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="G17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H17">
         <v>0.9</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>299</v>
+        <v>265</v>
       </c>
       <c r="K17" t="b">
         <f t="shared" si="0"/>
@@ -6583,19 +6538,19 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="G18" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H18">
         <v>0.9</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="K18" t="b">
         <f t="shared" si="0"/>
@@ -6613,25 +6568,25 @@
         <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>152</v>
+        <v>291</v>
       </c>
       <c r="G19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H19">
         <v>0.9</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K19" t="b">
         <f t="shared" si="0"/>
@@ -6649,25 +6604,25 @@
         <v>98</v>
       </c>
       <c r="D20" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="G20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H20">
         <v>0.9</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K20" t="b">
         <f t="shared" si="0"/>
@@ -6691,19 +6646,19 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>167</v>
+        <v>297</v>
       </c>
       <c r="G21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H21">
         <v>0.9</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K21" t="b">
         <f t="shared" si="0"/>
@@ -6727,19 +6682,19 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>168</v>
+        <v>296</v>
       </c>
       <c r="G22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H22">
         <v>0.9</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K22" t="b">
         <f t="shared" si="0"/>
@@ -6763,19 +6718,19 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>169</v>
+        <v>296</v>
       </c>
       <c r="G23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H23">
         <v>0.9</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K23" t="b">
         <f t="shared" si="0"/>
@@ -6799,26 +6754,26 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>170</v>
+        <v>290</v>
       </c>
       <c r="G24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H24">
         <v>0.9</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K24" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>99</v>
       </c>
@@ -6829,25 +6784,25 @@
         <v>100</v>
       </c>
       <c r="D25" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>172</v>
+        <v>298</v>
       </c>
       <c r="G25" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H25">
         <v>0.9</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="K25" t="b">
         <f t="shared" si="0"/>
@@ -6871,19 +6826,19 @@
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H26">
         <v>0.9</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K26" t="b">
         <f t="shared" si="0"/>
@@ -6907,19 +6862,19 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H27">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K27" t="b">
         <f t="shared" si="0"/>
@@ -6937,25 +6892,25 @@
         <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>174</v>
+        <v>299</v>
       </c>
       <c r="G28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H28">
         <v>0.9</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K28" t="b">
         <f t="shared" si="0"/>
@@ -6979,19 +6934,19 @@
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="G29" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="H29">
         <v>0.9</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c r="K29" t="b">
         <f t="shared" si="0"/>
@@ -7006,28 +6961,28 @@
         <v>2021</v>
       </c>
       <c r="C30" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="D30" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>179</v>
+        <v>300</v>
       </c>
       <c r="G30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H30">
         <v>0.9</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K30" t="b">
         <f t="shared" si="0"/>
@@ -7042,28 +6997,28 @@
         <v>2021</v>
       </c>
       <c r="C31" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="D31" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H31">
         <v>0.9</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K31" t="b">
         <f t="shared" si="0"/>
@@ -7087,19 +7042,19 @@
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="G32" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H32">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>303</v>
+        <v>269</v>
       </c>
       <c r="K32" t="b">
         <f t="shared" si="0"/>
@@ -7123,19 +7078,19 @@
         <v>0</v>
       </c>
       <c r="F33" t="s">
-        <v>183</v>
+        <v>301</v>
       </c>
       <c r="G33" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H33">
         <v>0.9</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K33" t="b">
         <f t="shared" si="0"/>
@@ -7159,19 +7114,19 @@
         <v>0</v>
       </c>
       <c r="F34" t="s">
-        <v>184</v>
+        <v>302</v>
       </c>
       <c r="G34" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H34">
         <v>1</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K34" t="b">
         <f t="shared" si="0"/>
@@ -7195,19 +7150,19 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>185</v>
+        <v>303</v>
       </c>
       <c r="G35" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="H35">
         <v>0.9</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="K35" t="b">
         <f t="shared" si="0"/>
@@ -7222,28 +7177,28 @@
         <v>2021</v>
       </c>
       <c r="C36" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="D36" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="G36" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H36">
         <v>0.9</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K36" t="b">
         <f t="shared" si="0"/>
@@ -7267,19 +7222,19 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="G37" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H37">
         <v>0.9</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>305</v>
+        <v>271</v>
       </c>
       <c r="K37" t="b">
         <f t="shared" si="0"/>
@@ -7303,19 +7258,19 @@
         <v>0</v>
       </c>
       <c r="F38" t="s">
-        <v>182</v>
+        <v>304</v>
       </c>
       <c r="G38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H38">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K38" t="b">
         <f t="shared" si="0"/>
@@ -7339,19 +7294,19 @@
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>190</v>
+        <v>305</v>
       </c>
       <c r="G39" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H39">
         <v>0.9</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="K39" t="b">
         <f t="shared" si="0"/>
@@ -7369,25 +7324,25 @@
         <v>125</v>
       </c>
       <c r="D40" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>161</v>
+        <v>292</v>
       </c>
       <c r="G40" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H40">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K40" t="b">
         <f t="shared" si="0"/>
@@ -7411,19 +7366,19 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H41">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K41" t="b">
         <f t="shared" si="0"/>
@@ -7447,19 +7402,19 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>192</v>
+        <v>306</v>
       </c>
       <c r="G42" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H42">
         <v>0.9</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>307</v>
+        <v>273</v>
       </c>
       <c r="K42" t="b">
         <f t="shared" si="0"/>
@@ -7477,32 +7432,32 @@
         <v>133</v>
       </c>
       <c r="D43" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H43">
         <v>0.95</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K43" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>81</v>
       </c>
@@ -7516,22 +7471,22 @@
         <v>83</v>
       </c>
       <c r="E44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>194</v>
+        <v>307</v>
       </c>
       <c r="G44" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="H44">
         <v>0.9</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>308</v>
+        <v>274</v>
       </c>
       <c r="K44" t="b">
         <f t="shared" si="0"/>
@@ -7555,19 +7510,19 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H45">
         <v>0.9</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K45" t="b">
         <f t="shared" si="0"/>
@@ -7585,25 +7540,25 @@
         <v>135</v>
       </c>
       <c r="D46" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="G46" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H46">
         <v>0.9</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K46" t="b">
         <f t="shared" si="0"/>
@@ -7612,34 +7567,34 @@
     </row>
     <row r="47" spans="1:11" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="B47">
         <v>2025</v>
       </c>
       <c r="C47" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>199</v>
+        <v>308</v>
       </c>
       <c r="G47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H47">
         <v>0.9</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K47" t="b">
         <f t="shared" si="0"/>
@@ -7648,34 +7603,34 @@
     </row>
     <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="B48">
         <v>2025</v>
       </c>
       <c r="C48" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="D48" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>203</v>
+        <v>139</v>
       </c>
       <c r="G48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H48">
         <v>0.9</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>309</v>
+        <v>275</v>
       </c>
       <c r="K48" t="b">
         <f t="shared" si="0"/>
@@ -7684,34 +7639,34 @@
     </row>
     <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="B49">
         <v>2025</v>
       </c>
       <c r="C49" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="D49" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>207</v>
+        <v>309</v>
       </c>
       <c r="G49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H49">
         <v>0.9</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K49" t="b">
         <f t="shared" si="0"/>
@@ -7720,34 +7675,34 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="B50">
         <v>2025</v>
       </c>
       <c r="C50" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="D50" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>203</v>
+        <v>310</v>
       </c>
       <c r="G50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H50">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>310</v>
+        <v>276</v>
       </c>
       <c r="K50" t="b">
         <f t="shared" si="0"/>
@@ -7756,34 +7711,34 @@
     </row>
     <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="B51">
         <v>2025</v>
       </c>
       <c r="C51" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="D51" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G51" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H51">
         <v>0.9</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K51" t="b">
         <f t="shared" si="0"/>
@@ -7792,34 +7747,34 @@
     </row>
     <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="B52">
         <v>2025</v>
       </c>
       <c r="C52" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="D52" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G52" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H52">
         <v>0.9</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K52" t="b">
         <f t="shared" si="0"/>
@@ -7828,34 +7783,34 @@
     </row>
     <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="B53">
         <v>2025</v>
       </c>
       <c r="C53" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="D53" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="E53" t="b">
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="G53" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H53">
         <v>0.8</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K53" t="b">
         <f t="shared" si="0"/>
@@ -7864,34 +7819,34 @@
     </row>
     <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="B54">
         <v>2025</v>
       </c>
       <c r="C54" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="D54" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="E54" t="b">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>224</v>
+        <v>311</v>
       </c>
       <c r="G54" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H54">
         <v>0.9</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>311</v>
+        <v>277</v>
       </c>
       <c r="K54" t="b">
         <f t="shared" si="0"/>
@@ -7900,34 +7855,34 @@
     </row>
     <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="B55">
         <v>2025</v>
       </c>
       <c r="C55" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="D55" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G55" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H55">
         <v>0.9</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K55" t="b">
         <f t="shared" si="0"/>
@@ -7936,34 +7891,34 @@
     </row>
     <row r="56" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="B56">
         <v>2025</v>
       </c>
       <c r="C56" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="G56" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H56">
         <v>0.9</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>312</v>
+        <v>278</v>
       </c>
       <c r="K56" t="b">
         <f t="shared" si="0"/>
@@ -7972,34 +7927,34 @@
     </row>
     <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="B57">
         <v>2025</v>
       </c>
       <c r="C57" t="s">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="D57" t="s">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="E57" t="b">
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>235</v>
+        <v>312</v>
       </c>
       <c r="G57" t="s">
-        <v>186</v>
+        <v>313</v>
       </c>
       <c r="H57">
         <v>0.9</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>313</v>
+        <v>279</v>
       </c>
       <c r="K57" t="b">
         <f t="shared" si="0"/>
@@ -8008,34 +7963,34 @@
     </row>
     <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="B58">
         <v>2025</v>
       </c>
       <c r="C58" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="D58" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="s">
-        <v>161</v>
+        <v>292</v>
       </c>
       <c r="G58" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H58">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K58" t="b">
         <f t="shared" si="0"/>
@@ -8044,34 +7999,34 @@
     </row>
     <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="B59">
         <v>2025</v>
       </c>
       <c r="C59" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="D59" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>169</v>
+        <v>296</v>
       </c>
       <c r="G59" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H59">
         <v>0.9</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K59" t="b">
         <f t="shared" si="0"/>
@@ -8080,34 +8035,34 @@
     </row>
     <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="B60">
         <v>2025</v>
       </c>
       <c r="C60" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="D60" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="E60" t="b">
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>245</v>
+        <v>314</v>
       </c>
       <c r="G60" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H60">
         <v>0.9</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>314</v>
+        <v>280</v>
       </c>
       <c r="K60" t="b">
         <f t="shared" si="0"/>
@@ -8116,34 +8071,34 @@
     </row>
     <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>246</v>
+        <v>217</v>
       </c>
       <c r="B61">
         <v>2020</v>
       </c>
       <c r="C61" t="s">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="D61" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="s">
-        <v>249</v>
+        <v>296</v>
       </c>
       <c r="G61" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H61">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K61" t="b">
         <f t="shared" si="0"/>
@@ -8152,34 +8107,34 @@
     </row>
     <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="B62">
         <v>2020</v>
       </c>
       <c r="C62" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="D62" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="G62" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H62">
         <v>0.9</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K62" t="b">
         <f t="shared" si="0"/>
@@ -8188,34 +8143,34 @@
     </row>
     <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="B63">
         <v>2020</v>
       </c>
       <c r="C63" t="s">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="D63" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G63" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H63">
         <v>0.9</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K63" t="b">
         <f t="shared" si="0"/>
@@ -8224,34 +8179,34 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="B64">
         <v>2020</v>
       </c>
       <c r="C64" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
       <c r="D64" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
       </c>
       <c r="F64" t="s">
+        <v>315</v>
+      </c>
+      <c r="G64" t="s">
+        <v>138</v>
+      </c>
+      <c r="H64">
+        <v>0.9</v>
+      </c>
+      <c r="I64" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="G64" t="s">
-        <v>139</v>
-      </c>
-      <c r="H64">
-        <v>0.9</v>
-      </c>
-      <c r="I64" s="5" t="s">
-        <v>293</v>
-      </c>
       <c r="J64" s="5" t="s">
-        <v>315</v>
+        <v>281</v>
       </c>
       <c r="K64" t="b">
         <f t="shared" si="0"/>
@@ -8260,34 +8215,34 @@
     </row>
     <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>260</v>
+        <v>229</v>
       </c>
       <c r="B65">
         <v>2020</v>
       </c>
       <c r="C65" t="s">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="D65" t="s">
-        <v>262</v>
+        <v>231</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G65" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H65">
         <v>0.9</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K65" t="b">
         <f t="shared" si="0"/>
@@ -8296,34 +8251,34 @@
     </row>
     <row r="66" spans="1:11" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="B66">
         <v>2022</v>
       </c>
       <c r="C66" t="s">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G66" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H66">
         <v>0.9</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K66" t="b">
         <f t="shared" si="0"/>
@@ -8332,34 +8287,34 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>266</v>
+        <v>235</v>
       </c>
       <c r="B67">
         <v>2022</v>
       </c>
       <c r="C67" t="s">
-        <v>267</v>
+        <v>236</v>
       </c>
       <c r="D67" t="s">
-        <v>268</v>
+        <v>237</v>
       </c>
       <c r="E67" t="b">
         <v>0</v>
       </c>
       <c r="F67" t="s">
-        <v>269</v>
+        <v>238</v>
       </c>
       <c r="G67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H67">
         <v>0.9</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>316</v>
+        <v>282</v>
       </c>
       <c r="K67" t="b">
         <f t="shared" ref="K67:K72" si="1">IF(I67="EXCLUDE",FALSE,TRUE)</f>
@@ -8368,34 +8323,34 @@
     </row>
     <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
       <c r="B68">
         <v>2022</v>
       </c>
       <c r="C68" t="s">
-        <v>271</v>
+        <v>240</v>
       </c>
       <c r="D68" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
       </c>
       <c r="F68" t="s">
-        <v>138</v>
+        <v>291</v>
       </c>
       <c r="G68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H68">
         <v>0.95</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K68" t="b">
         <f t="shared" si="1"/>
@@ -8404,34 +8359,34 @@
     </row>
     <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>273</v>
+        <v>242</v>
       </c>
       <c r="B69">
         <v>2022</v>
       </c>
       <c r="C69" t="s">
-        <v>274</v>
+        <v>243</v>
       </c>
       <c r="D69" t="s">
-        <v>275</v>
+        <v>244</v>
       </c>
       <c r="E69" t="b">
         <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>276</v>
+        <v>245</v>
       </c>
       <c r="G69" t="s">
-        <v>277</v>
+        <v>167</v>
       </c>
       <c r="H69">
         <v>0.9</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>317</v>
+        <v>283</v>
       </c>
       <c r="K69" t="b">
         <f t="shared" si="1"/>
@@ -8440,34 +8395,34 @@
     </row>
     <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="B70">
         <v>2022</v>
       </c>
       <c r="C70" t="s">
-        <v>279</v>
+        <v>247</v>
       </c>
       <c r="D70" t="s">
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="G70" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H70">
         <v>0.9</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K70" t="b">
         <f t="shared" si="1"/>
@@ -8476,34 +8431,34 @@
     </row>
     <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>282</v>
+        <v>249</v>
       </c>
       <c r="B71">
         <v>2022</v>
       </c>
       <c r="C71" t="s">
-        <v>283</v>
+        <v>250</v>
       </c>
       <c r="D71" t="s">
-        <v>284</v>
+        <v>251</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>169</v>
+        <v>296</v>
       </c>
       <c r="G71" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H71">
         <v>0.9</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K71" t="b">
         <f t="shared" si="1"/>
@@ -8512,34 +8467,34 @@
     </row>
     <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>285</v>
+        <v>252</v>
       </c>
       <c r="B72">
         <v>2022</v>
       </c>
       <c r="C72" t="s">
-        <v>286</v>
+        <v>253</v>
       </c>
       <c r="D72" t="s">
-        <v>287</v>
+        <v>254</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72" t="s">
-        <v>288</v>
+        <v>316</v>
       </c>
       <c r="G72" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H72">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="K72" t="b">
         <f t="shared" si="1"/>
@@ -8595,10 +8550,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>318</v>
+        <v>284</v>
       </c>
       <c r="C2" t="s">
-        <v>319</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -8607,7 +8562,7 @@
       </c>
       <c r="B3">
         <f>COUNTIFS('Merged results table'!E:E,TRUE,'Merged results table'!K:K,TRUE)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <f>COUNTIFS('Merged results table'!E:E,TRUE,'Merged results table'!K:K,FALSE)</f>
@@ -8620,7 +8575,7 @@
       </c>
       <c r="B4">
         <f>COUNTIFS('Merged results table'!E:E,FALSE,'Merged results table'!K:K,TRUE)</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <f>COUNTIFS('Merged results table'!E:E,FALSE,'Merged results table'!K:K,FALSE)</f>
@@ -8633,7 +8588,7 @@
       </c>
       <c r="B6">
         <f>B3</f>
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -8660,7 +8615,7 @@
       </c>
       <c r="B9">
         <f>B4</f>
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -8669,7 +8624,7 @@
       </c>
       <c r="B11">
         <f>(B3+C4)/(B3+B4+C3+C4)</f>
-        <v>0.85915492957746475</v>
+        <v>0.90140845070422537</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -8678,7 +8633,7 @@
       </c>
       <c r="B12">
         <f>B3/(B3+B4)</f>
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">

--- a/Screen_7_Cash_Releasing_Benefit/validation_data/stage_7_validation_workbook_full.xlsx
+++ b/Screen_7_Cash_Releasing_Benefit/validation_data/stage_7_validation_workbook_full.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nhs-my.sharepoint.com/personal/oliver_carey1_nhs_net/Documents/Documents/Projects/NHSCRB/Screen_7_Cash_Releasing_Benefit/validation_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{EF267FAC-E7CE-4906-8934-5AE241006237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{607D2B70-C5E0-4BFA-A9A3-1AF09E5C3831}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="8_{EF267FAC-E7CE-4906-8934-5AE241006237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5DD239D-BC2B-49F7-9BE1-B52A337BACF5}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{66513E08-89B8-4D61-A86D-819C01466699}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{66513E08-89B8-4D61-A86D-819C01466699}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage_7_API" sheetId="1" r:id="rId1"/>
     <sheet name="ID_Lookup" sheetId="5" r:id="rId2"/>
-    <sheet name="Stage_7_OC" sheetId="6" r:id="rId3"/>
-    <sheet name="Merged results table" sheetId="3" r:id="rId4"/>
-    <sheet name="Evaluating Results" sheetId="4" r:id="rId5"/>
+    <sheet name="Stage_7_AA" sheetId="7" r:id="rId3"/>
+    <sheet name="Stage_7_OC" sheetId="6" r:id="rId4"/>
+    <sheet name="Merged results table" sheetId="3" r:id="rId5"/>
+    <sheet name="Evaluating Results" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Merged results table'!$A$1:$K$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Merged results table'!$A$1:$N$72</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1849" uniqueCount="351">
   <si>
     <t>id</t>
   </si>
@@ -1395,12 +1396,114 @@
   <si>
     <t>The article only reports cost-effectiveness (ICER) without explicit savings.</t>
   </si>
+  <si>
+    <t>include_stage_7 (Akkshata)</t>
+  </si>
+  <si>
+    <t>Exclude</t>
+  </si>
+  <si>
+    <t>no cost impact</t>
+  </si>
+  <si>
+    <t>Include</t>
+  </si>
+  <si>
+    <t>cost saving</t>
+  </si>
+  <si>
+    <t>cost effectiveness critieria currently not met</t>
+  </si>
+  <si>
+    <t>cost savings</t>
+  </si>
+  <si>
+    <t>Incremental cost saving per person was 18.75</t>
+  </si>
+  <si>
+    <t>saving of 53,000/100 patients</t>
+  </si>
+  <si>
+    <t>incremental costeffectiveness ratio (ICER) of 12,659 per QALY gained</t>
+  </si>
+  <si>
+    <t>early-supported discharge is safe and cost-effective but no actual cost impact</t>
+  </si>
+  <si>
+    <t>provides evidence that the NBRPP results in substantial cost saving through reducing; admissions for back pain</t>
+  </si>
+  <si>
+    <t>10% reduction in costs</t>
+  </si>
+  <si>
+    <t>risk-based screening at a 4% 10-year absolute risk threshold was cost-effective in 48.4% and 57.4% of the simulations at willingness-to-pay thresholds of GBP20,000 (US$26,000) and 30,000 ($39,386) per QALY, respectively.</t>
+  </si>
+  <si>
+    <t>Potential cumulative direct cost savings achievable in the modelled population were estimated at 687 m over 5 years (5,585/person), with total (direct and indirect) savings of 1,034 m (8,400/person)</t>
+  </si>
+  <si>
+    <t>Incremental cost-effectiveness was calculated using a Markov population cohort simulation</t>
+  </si>
+  <si>
+    <t>reduction in hospital admission</t>
+  </si>
+  <si>
+    <t>estimated per-patient cost saving of 179.16</t>
+  </si>
+  <si>
+    <t>cost (16 million 2015-16; 11 million 2018-19)</t>
+  </si>
+  <si>
+    <t>incurred 414 fewer bed days (303 vs 717), and re-admitted at a lower rate (5% vs 11%)</t>
+  </si>
+  <si>
+    <t>Incremental cost effectiveness ratios (ICERs) and net monetary benefit from UK healthcare and societal perspectives are reported.</t>
+  </si>
+  <si>
+    <t>Specifically, savings from avoided ED visits ranged from 22,225 to 43,435 per 100 patients, with additional savings from early detection of SSIs and prevention of antibiotic resistance estimated at 27,909 per 100 patients</t>
+  </si>
+  <si>
+    <t>lower treatment costs</t>
+  </si>
+  <si>
+    <t>negative point estimate for incremental costs (-796; 95% CI -2016 to 424) and positive point estimate for incremental QALYs (0.009, -0.021 to 0.039)</t>
+  </si>
+  <si>
+    <t>The mean incremental cost-effectiveness ratio (ICER per quality adjusted life year (QALY) saved, 50-year time horizon; 3.5% discount rate) of SQ (assumes counterfactual of no treatment scale-up post-2015)</t>
+  </si>
+  <si>
+    <t>PRA was cost-effective in specific situations compared with CRA in the UK for assessment of women with or without GPVs in BC and OC susceptibility genes.</t>
+  </si>
+  <si>
+    <t>strategies demonstrated cost-effectiveness relative to SoC with total cost per patient of GBP 983.37 for FIB-4/TE, GBP 993.15 for FIB-4/ELF compared to SoC, GBP 1,014.15.</t>
+  </si>
+  <si>
+    <t>Machine learning was leveraged to successfully reduce the number of normal mammograms that radiologists need to read without degrading diagnostic accuracy</t>
+  </si>
+  <si>
+    <t>The economic analysis revealed some indication of reduced resource use/costs associated with the intervention</t>
+  </si>
+  <si>
+    <t>The GtACH programme significantly reduced the falls rate in the study care homes</t>
+  </si>
+  <si>
+    <t>cost savings predicted</t>
+  </si>
+  <si>
+    <t>no evidence of cost impact</t>
+  </si>
+  <si>
+    <t>AA_Include</t>
+  </si>
+  <si>
+    <t>AA_Exclude</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1448,6 +1551,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1469,7 +1593,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1482,6 +1606,10 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4168,6 +4296,1739 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{110CA747-4A74-4E3D-B58F-A6AF04ACC87D}">
+  <dimension ref="A1:G72"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="G1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>2019</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G2" t="b">
+        <f>IF(E2="EXCLUDE",FALSE,TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>2019</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G3" t="b">
+        <f t="shared" ref="G3:G66" si="0">IF(E3="EXCLUDE",FALSE,TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>2019</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>2019</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>2019</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="G6" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>2019</v>
+      </c>
+      <c r="C7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G7" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8">
+        <v>2019</v>
+      </c>
+      <c r="C8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G8" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>2019</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G9" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>2019</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="G10" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <v>2019</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G11" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
+        <v>2019</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="G12" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13">
+        <v>2019</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="G13" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14">
+        <v>2019</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="G14" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15">
+        <v>2019</v>
+      </c>
+      <c r="C15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="G15" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16">
+        <v>2019</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G16" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17">
+        <v>2019</v>
+      </c>
+      <c r="C17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" t="s">
+        <v>153</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="G17" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18">
+        <v>2019</v>
+      </c>
+      <c r="C18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="G18" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19">
+        <v>2019</v>
+      </c>
+      <c r="C19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" t="s">
+        <v>156</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G19" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20">
+        <v>2019</v>
+      </c>
+      <c r="C20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" t="s">
+        <v>157</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G20" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21">
+        <v>2019</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G21" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22">
+        <v>2019</v>
+      </c>
+      <c r="C22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G22" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23">
+        <v>2019</v>
+      </c>
+      <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="G23" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24">
+        <v>2019</v>
+      </c>
+      <c r="C24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G24" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25">
+        <v>2019</v>
+      </c>
+      <c r="C25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="G25" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26">
+        <v>2021</v>
+      </c>
+      <c r="C26" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G26" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27">
+        <v>2021</v>
+      </c>
+      <c r="C27" t="s">
+        <v>102</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G27" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28">
+        <v>2021</v>
+      </c>
+      <c r="C28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" t="s">
+        <v>160</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G28" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29">
+        <v>2021</v>
+      </c>
+      <c r="C29" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="G29" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30">
+        <v>2021</v>
+      </c>
+      <c r="C30" t="s">
+        <v>162</v>
+      </c>
+      <c r="D30" t="s">
+        <v>163</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G30" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31">
+        <v>2021</v>
+      </c>
+      <c r="C31" t="s">
+        <v>164</v>
+      </c>
+      <c r="D31" t="s">
+        <v>165</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G31" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32">
+        <v>2021</v>
+      </c>
+      <c r="C32" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="G32" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33">
+        <v>2021</v>
+      </c>
+      <c r="C33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G33" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34">
+        <v>2021</v>
+      </c>
+      <c r="C34" t="s">
+        <v>112</v>
+      </c>
+      <c r="D34" t="s">
+        <v>113</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G34" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>114</v>
+      </c>
+      <c r="B35">
+        <v>2021</v>
+      </c>
+      <c r="C35" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="G35" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36">
+        <v>2021</v>
+      </c>
+      <c r="C36" t="s">
+        <v>168</v>
+      </c>
+      <c r="D36" t="s">
+        <v>169</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G36" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37">
+        <v>2021</v>
+      </c>
+      <c r="C37" t="s">
+        <v>119</v>
+      </c>
+      <c r="D37" t="s">
+        <v>120</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="G37" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38">
+        <v>2021</v>
+      </c>
+      <c r="C38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" t="s">
+        <v>80</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G38" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39">
+        <v>2021</v>
+      </c>
+      <c r="C39" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" t="s">
+        <v>123</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G39" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>124</v>
+      </c>
+      <c r="B40">
+        <v>2021</v>
+      </c>
+      <c r="C40" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" t="s">
+        <v>171</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G40" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>126</v>
+      </c>
+      <c r="B41">
+        <v>2025</v>
+      </c>
+      <c r="C41" t="s">
+        <v>127</v>
+      </c>
+      <c r="D41" t="s">
+        <v>128</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G41" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>129</v>
+      </c>
+      <c r="B42">
+        <v>2025</v>
+      </c>
+      <c r="C42" t="s">
+        <v>130</v>
+      </c>
+      <c r="D42" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="G42" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>132</v>
+      </c>
+      <c r="B43">
+        <v>2025</v>
+      </c>
+      <c r="C43" t="s">
+        <v>133</v>
+      </c>
+      <c r="D43" t="s">
+        <v>172</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G43" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44">
+        <v>2025</v>
+      </c>
+      <c r="C44" t="s">
+        <v>82</v>
+      </c>
+      <c r="D44" t="s">
+        <v>83</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="G44" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45">
+        <v>2025</v>
+      </c>
+      <c r="C45" t="s">
+        <v>85</v>
+      </c>
+      <c r="D45" t="s">
+        <v>86</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G45" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>134</v>
+      </c>
+      <c r="B46">
+        <v>2025</v>
+      </c>
+      <c r="C46" t="s">
+        <v>135</v>
+      </c>
+      <c r="D46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G46" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>174</v>
+      </c>
+      <c r="B47">
+        <v>2025</v>
+      </c>
+      <c r="C47" t="s">
+        <v>175</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G47" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>177</v>
+      </c>
+      <c r="B48">
+        <v>2025</v>
+      </c>
+      <c r="C48" t="s">
+        <v>178</v>
+      </c>
+      <c r="D48" t="s">
+        <v>179</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G48" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>180</v>
+      </c>
+      <c r="B49">
+        <v>2025</v>
+      </c>
+      <c r="C49" t="s">
+        <v>181</v>
+      </c>
+      <c r="D49" t="s">
+        <v>182</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G49" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>183</v>
+      </c>
+      <c r="B50">
+        <v>2025</v>
+      </c>
+      <c r="C50" t="s">
+        <v>184</v>
+      </c>
+      <c r="D50" t="s">
+        <v>185</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G50" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>186</v>
+      </c>
+      <c r="B51">
+        <v>2025</v>
+      </c>
+      <c r="C51" t="s">
+        <v>187</v>
+      </c>
+      <c r="D51" t="s">
+        <v>188</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G51" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>189</v>
+      </c>
+      <c r="B52">
+        <v>2025</v>
+      </c>
+      <c r="C52" t="s">
+        <v>190</v>
+      </c>
+      <c r="D52" t="s">
+        <v>191</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G52" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>192</v>
+      </c>
+      <c r="B53">
+        <v>2025</v>
+      </c>
+      <c r="C53" t="s">
+        <v>193</v>
+      </c>
+      <c r="D53" t="s">
+        <v>194</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G53" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>196</v>
+      </c>
+      <c r="B54">
+        <v>2025</v>
+      </c>
+      <c r="C54" t="s">
+        <v>197</v>
+      </c>
+      <c r="D54" t="s">
+        <v>198</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="G54" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>199</v>
+      </c>
+      <c r="B55">
+        <v>2025</v>
+      </c>
+      <c r="C55" t="s">
+        <v>200</v>
+      </c>
+      <c r="D55" t="s">
+        <v>201</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G55" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>202</v>
+      </c>
+      <c r="B56">
+        <v>2025</v>
+      </c>
+      <c r="C56" t="s">
+        <v>203</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="G56" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>205</v>
+      </c>
+      <c r="B57">
+        <v>2025</v>
+      </c>
+      <c r="C57" t="s">
+        <v>206</v>
+      </c>
+      <c r="D57" t="s">
+        <v>207</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="G57" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>208</v>
+      </c>
+      <c r="B58">
+        <v>2025</v>
+      </c>
+      <c r="C58" t="s">
+        <v>209</v>
+      </c>
+      <c r="D58" t="s">
+        <v>210</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="G58" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>211</v>
+      </c>
+      <c r="B59">
+        <v>2025</v>
+      </c>
+      <c r="C59" t="s">
+        <v>212</v>
+      </c>
+      <c r="D59" t="s">
+        <v>213</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="G59" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>214</v>
+      </c>
+      <c r="B60">
+        <v>2025</v>
+      </c>
+      <c r="C60" t="s">
+        <v>215</v>
+      </c>
+      <c r="D60" t="s">
+        <v>216</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="G60" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>217</v>
+      </c>
+      <c r="B61">
+        <v>2020</v>
+      </c>
+      <c r="C61" t="s">
+        <v>218</v>
+      </c>
+      <c r="D61" t="s">
+        <v>219</v>
+      </c>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>220</v>
+      </c>
+      <c r="B62">
+        <v>2020</v>
+      </c>
+      <c r="C62" t="s">
+        <v>221</v>
+      </c>
+      <c r="D62" t="s">
+        <v>222</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G62" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>223</v>
+      </c>
+      <c r="B63">
+        <v>2020</v>
+      </c>
+      <c r="C63" t="s">
+        <v>224</v>
+      </c>
+      <c r="D63" t="s">
+        <v>225</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G63" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>226</v>
+      </c>
+      <c r="B64">
+        <v>2020</v>
+      </c>
+      <c r="C64" t="s">
+        <v>227</v>
+      </c>
+      <c r="D64" t="s">
+        <v>228</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="G64" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>229</v>
+      </c>
+      <c r="B65">
+        <v>2020</v>
+      </c>
+      <c r="C65" t="s">
+        <v>230</v>
+      </c>
+      <c r="D65" t="s">
+        <v>231</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G65" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>232</v>
+      </c>
+      <c r="B66">
+        <v>2022</v>
+      </c>
+      <c r="C66" t="s">
+        <v>233</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="G66" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>235</v>
+      </c>
+      <c r="B67">
+        <v>2022</v>
+      </c>
+      <c r="C67" t="s">
+        <v>236</v>
+      </c>
+      <c r="D67" t="s">
+        <v>237</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="G67" t="b">
+        <f t="shared" ref="G67:G72" si="1">IF(E67="EXCLUDE",FALSE,TRUE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>239</v>
+      </c>
+      <c r="B68">
+        <v>2022</v>
+      </c>
+      <c r="C68" t="s">
+        <v>240</v>
+      </c>
+      <c r="D68" t="s">
+        <v>241</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G68" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>242</v>
+      </c>
+      <c r="B69">
+        <v>2022</v>
+      </c>
+      <c r="C69" t="s">
+        <v>243</v>
+      </c>
+      <c r="D69" t="s">
+        <v>244</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="G69" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>246</v>
+      </c>
+      <c r="B70">
+        <v>2022</v>
+      </c>
+      <c r="C70" t="s">
+        <v>247</v>
+      </c>
+      <c r="D70" t="s">
+        <v>248</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G70" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>249</v>
+      </c>
+      <c r="B71">
+        <v>2022</v>
+      </c>
+      <c r="C71" t="s">
+        <v>250</v>
+      </c>
+      <c r="D71" t="s">
+        <v>251</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G71" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>252</v>
+      </c>
+      <c r="B72">
+        <v>2022</v>
+      </c>
+      <c r="C72" t="s">
+        <v>253</v>
+      </c>
+      <c r="D72" t="s">
+        <v>254</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G72" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0EE19B4-BBB1-4308-87AE-8E39EAC2CFC3}">
   <dimension ref="A1:G72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5904,13 +7765,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1235A4A9-643F-403F-8F39-91437DA8F632}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5944,8 +7804,17 @@
       <c r="K1" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L1" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="N1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -5980,8 +7849,18 @@
         <f>IF(I2="EXCLUDE",FALSE,TRUE)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L2" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N2" t="b">
+        <f>IF(L2="EXCLUDE",FALSE,TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6016,8 +7895,18 @@
         <f t="shared" ref="K3:K66" si="0">IF(I3="EXCLUDE",FALSE,TRUE)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L3" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N3" t="b">
+        <f t="shared" ref="N3:N66" si="1">IF(L3="EXCLUDE",FALSE,TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -6052,8 +7941,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L4" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N4" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -6088,8 +7987,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L5" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -6124,8 +8033,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L6" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="N6" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -6160,8 +8079,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L7" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N7" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -6196,8 +8125,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L8" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N8" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -6232,8 +8171,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L9" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N9" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -6268,8 +8217,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L10" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="N10" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -6304,8 +8263,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L11" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N11" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -6340,8 +8309,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L12" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="N12" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -6376,8 +8355,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L13" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="N13" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -6412,8 +8401,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L14" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="N14" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>87</v>
       </c>
@@ -6445,11 +8444,20 @@
         <v>264</v>
       </c>
       <c r="K15" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="N15" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -6484,8 +8492,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L16" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N16" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>90</v>
       </c>
@@ -6520,8 +8538,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L17" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="N17" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -6556,8 +8584,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L18" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="N18" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>95</v>
       </c>
@@ -6592,8 +8630,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L19" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N19" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>97</v>
       </c>
@@ -6628,8 +8676,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L20" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N20" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -6664,8 +8722,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L21" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N21" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>60</v>
       </c>
@@ -6697,11 +8765,20 @@
         <v>257</v>
       </c>
       <c r="K22" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="N22" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>63</v>
       </c>
@@ -6733,11 +8810,20 @@
         <v>257</v>
       </c>
       <c r="K23" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="N23" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -6772,8 +8858,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L24" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N24" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>99</v>
       </c>
@@ -6808,8 +8904,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L25" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="N25" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>69</v>
       </c>
@@ -6844,8 +8950,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L26" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N26" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>101</v>
       </c>
@@ -6880,8 +8996,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L27" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N27" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>104</v>
       </c>
@@ -6916,8 +9042,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L28" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N28" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>106</v>
       </c>
@@ -6952,8 +9088,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L29" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="N29" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>109</v>
       </c>
@@ -6988,8 +9134,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L30" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N30" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>110</v>
       </c>
@@ -7024,8 +9180,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L31" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N31" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -7060,8 +9226,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L32" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="N32" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -7096,8 +9272,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L33" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N33" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>111</v>
       </c>
@@ -7132,8 +9318,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L34" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M34" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N34" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>114</v>
       </c>
@@ -7168,8 +9364,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L35" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="N35" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>117</v>
       </c>
@@ -7204,8 +9410,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L36" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M36" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N36" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>118</v>
       </c>
@@ -7240,8 +9456,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L37" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="N37" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>78</v>
       </c>
@@ -7276,8 +9502,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L38" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N38" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>121</v>
       </c>
@@ -7309,11 +9545,20 @@
         <v>272</v>
       </c>
       <c r="K39" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N39" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>124</v>
       </c>
@@ -7348,8 +9593,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L40" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M40" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N40" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>126</v>
       </c>
@@ -7384,8 +9639,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L41" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M41" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N41" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>129</v>
       </c>
@@ -7420,8 +9685,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L42" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="N42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>132</v>
       </c>
@@ -7456,8 +9731,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L43" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N43" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>81</v>
       </c>
@@ -7492,8 +9777,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L44" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="N44" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>84</v>
       </c>
@@ -7528,8 +9823,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L45" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N45" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>134</v>
       </c>
@@ -7564,8 +9869,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L46" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M46" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N46" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>174</v>
       </c>
@@ -7600,8 +9915,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L47" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M47" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N47" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>177</v>
       </c>
@@ -7636,8 +9961,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L48" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M48" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N48" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>180</v>
       </c>
@@ -7672,8 +10007,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L49" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M49" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N49" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>183</v>
       </c>
@@ -7705,11 +10050,20 @@
         <v>276</v>
       </c>
       <c r="K50" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M50" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N50" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>186</v>
       </c>
@@ -7744,8 +10098,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L51" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M51" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N51" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>189</v>
       </c>
@@ -7780,8 +10144,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L52" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M52" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N52" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>192</v>
       </c>
@@ -7816,8 +10190,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L53" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M53" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N53" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>196</v>
       </c>
@@ -7852,8 +10236,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L54" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="N54" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>199</v>
       </c>
@@ -7888,8 +10282,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="L55" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M55" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N55" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>202</v>
       </c>
@@ -7924,8 +10328,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L56" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M56" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="N56" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>205</v>
       </c>
@@ -7960,8 +10374,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L57" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M57" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="N57" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>208</v>
       </c>
@@ -7993,11 +10417,20 @@
         <v>257</v>
       </c>
       <c r="K58" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="L58" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="N58" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>211</v>
       </c>
@@ -8032,8 +10465,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L59" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M59" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="N59" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>214</v>
       </c>
@@ -8068,8 +10511,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L60" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="N60" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>217</v>
       </c>
@@ -8104,8 +10557,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>220</v>
       </c>
@@ -8140,8 +10599,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L62" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M62" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N62" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>223</v>
       </c>
@@ -8176,8 +10645,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L63" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M63" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N63" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>226</v>
       </c>
@@ -8212,8 +10691,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L64" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="N64" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>229</v>
       </c>
@@ -8248,8 +10737,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="L65" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M65" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N65" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>232</v>
       </c>
@@ -8284,8 +10783,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L66" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="N66" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>235</v>
       </c>
@@ -8317,11 +10826,21 @@
         <v>282</v>
       </c>
       <c r="K67" t="b">
-        <f t="shared" ref="K67:K72" si="1">IF(I67="EXCLUDE",FALSE,TRUE)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="K67:K72" si="2">IF(I67="EXCLUDE",FALSE,TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="L67" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M67" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="N67" t="b">
+        <f t="shared" ref="N67:N72" si="3">IF(L67="EXCLUDE",FALSE,TRUE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>239</v>
       </c>
@@ -8353,11 +10872,21 @@
         <v>257</v>
       </c>
       <c r="K68" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L68" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M68" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N68" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>242</v>
       </c>
@@ -8389,11 +10918,21 @@
         <v>283</v>
       </c>
       <c r="K69" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L69" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="M69" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="N69" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>246</v>
       </c>
@@ -8425,11 +10964,21 @@
         <v>257</v>
       </c>
       <c r="K70" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L70" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M70" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="N70" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>249</v>
       </c>
@@ -8461,11 +11010,21 @@
         <v>257</v>
       </c>
       <c r="K71" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L71" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M71" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="N71" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>252</v>
       </c>
@@ -8497,23 +11056,21 @@
         <v>257</v>
       </c>
       <c r="K72" t="b">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L72" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="M72" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="N72" t="b">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K72" xr:uid="{1235A4A9-643F-403F-8F39-91437DA8F632}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="FALSE"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="10">
-      <filters>
-        <filter val="TRUE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <conditionalFormatting sqref="M10">
     <cfRule type="containsText" dxfId="9" priority="8" operator="containsText" text="Exclude">
       <formula>NOT(ISERROR(SEARCH("Exclude",M10)))</formula>
@@ -8534,114 +11091,277 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60927BCB-4710-4D9A-A38E-921B487297AE}">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
+      <c r="E1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="F2" t="s">
+        <v>349</v>
+      </c>
+      <c r="G2" t="s">
+        <v>350</v>
+      </c>
+      <c r="J2" t="s">
+        <v>349</v>
+      </c>
+      <c r="K2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <f>COUNTIFS('Merged results table'!E:E,TRUE,'Merged results table'!K:K,TRUE)</f>
-        <v>15</v>
-      </c>
-      <c r="C3">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2">
         <f>COUNTIFS('Merged results table'!E:E,TRUE,'Merged results table'!K:K,FALSE)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3">
+        <f>COUNTIFS('Merged results table'!E:E,TRUE,'Merged results table'!N:N,TRUE)</f>
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <f>COUNTIFS('Merged results table'!E:E,TRUE,'Merged results table'!N:N,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>284</v>
+      </c>
+      <c r="J3">
+        <f>COUNTIFS('Merged results table'!K:K,TRUE,'Merged results table'!N:N,TRUE)</f>
+        <v>23</v>
+      </c>
+      <c r="K3">
+        <f>COUNTIFS('Merged results table'!K:K,TRUE,'Merged results table'!N:N,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <f>COUNTIFS('Merged results table'!E:E,FALSE,'Merged results table'!K:K,TRUE)</f>
-        <v>6</v>
-      </c>
-      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2">
         <f>COUNTIFS('Merged results table'!E:E,FALSE,'Merged results table'!K:K,FALSE)</f>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4">
+        <f>COUNTIFS('Merged results table'!E:E,FALSE,'Merged results table'!N:N,TRUE)</f>
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <f>COUNTIFS('Merged results table'!E:E,FALSE,'Merged results table'!N:N,FALSE)</f>
+        <v>43</v>
+      </c>
+      <c r="I4" t="s">
+        <v>285</v>
+      </c>
+      <c r="J4">
+        <f>COUNTIFS('Merged results table'!K:K,FALSE,'Merged results table'!N:N,TRUE)</f>
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <f>COUNTIFS('Merged results table'!K:K,FALSE,'Merged results table'!N:N,FALSE)</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <f>B3</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6">
+        <f>F3</f>
+        <v>14</v>
+      </c>
+      <c r="I6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6">
+        <f>J3</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <f>C4</f>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <f>G4</f>
+        <v>43</v>
+      </c>
+      <c r="I7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7">
+        <f>K4</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <f>C3</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8">
+        <f>G3</f>
+        <v>2</v>
+      </c>
+      <c r="I8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8">
+        <f>K3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <f>B4</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9">
+        <f>F4</f>
+        <v>12</v>
+      </c>
+      <c r="I9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9">
+        <f>J4</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <f>(B3+C4)/(B3+B4+C3+C4)</f>
-        <v>0.90140845070422537</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+        <v>0.84507042253521125</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11">
+        <f>(F3+G4)/(F3+F4+G3+G4)</f>
+        <v>0.80281690140845074</v>
+      </c>
+      <c r="I11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11">
+        <f>(J3+K4)/(J3+J4+K3+K4)</f>
+        <v>0.95774647887323938</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
         <f>B3/(B3+B4)</f>
-        <v>0.7142857142857143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+        <v>0.60869565217391308</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12">
+        <f>F3/(F3+F4)</f>
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="I12" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12">
+        <f>J3/(J3+J4)</f>
+        <v>0.88461538461538458</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>53</v>
       </c>
